--- a/input/timetable/Педиатрия.xlsx
+++ b/input/timetable/Педиатрия.xlsx
@@ -235,15 +235,6 @@
     <t>Сестринское дело в педиатрии, п/г 1, СОКЦОМиД</t>
   </si>
   <si>
-    <t>Гигиена, п/г 1, А439</t>
-  </si>
-  <si>
-    <t>А439----------------А632</t>
-  </si>
-  <si>
-    <t>Гигиена, п/г 2, А439</t>
-  </si>
-  <si>
     <t>Нормальная физиология, п/г 1, А433</t>
   </si>
   <si>
@@ -466,9 +457,6 @@
     <t>Правоведение (пр), А615</t>
   </si>
   <si>
-    <t>А439---------------</t>
-  </si>
-  <si>
     <t>Биохимия, п/г 2, А424</t>
   </si>
   <si>
@@ -635,9 +623,6 @@
   </si>
   <si>
     <t>Биохимия, п/г 1, ЭОиДОТ</t>
-  </si>
-  <si>
-    <t>Поликлиническая и неотложная педиатрия (лекция 16 ч), ЭОиДОТ // Д етская хирургия (лекция 16 ч), СГКБ</t>
   </si>
   <si>
     <t>А25'---------------------СОКБ</t>
@@ -676,6 +661,21 @@
       </rPr>
       <t>: 1. ПДБ - 'Пропедевтика детских болезней.  ПВБ - 'Пропедевтика внутренних болезней.                                            2. Элект. дисциплины по физич. культуре и спорту проводятся  1 парой или  2 парой в зависимости от выбранной элективной дисциплины., занятия в объеме 16 часов провдятся по отдельному расписанию.</t>
     </r>
+  </si>
+  <si>
+    <t>Поликлиническая и неотложная педиатрия (лекция 16 ч), ЭОиДОТ // Д етская хирургия (лекция 16 ч),ЭОиДОТ</t>
+  </si>
+  <si>
+    <t>Гигиена, п/г 1, А431</t>
+  </si>
+  <si>
+    <t>А431----------------А632</t>
+  </si>
+  <si>
+    <t>А431---------------</t>
+  </si>
+  <si>
+    <t>Гигиена, п/г 2, А431</t>
   </si>
 </sst>
 </file>
@@ -1770,79 +1770,317 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="47" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1852,23 +2090,16 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1879,429 +2110,101 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="47" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="37" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="21" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="37" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="22" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="35" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="37" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="38" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="39" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="21" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="22" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="21" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="23" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="24" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="25" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="58" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="25" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="26" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="23" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="26" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="22" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="22" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="27" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="21" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="35" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="22" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="38" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="38" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="39" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="37" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="22" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="21" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="22" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="26" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="49" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="37" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="37" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2333,8 +2236,21 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="39" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -2345,64 +2261,233 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="24" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="25" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="23" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="24" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="25" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="58" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="25" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="26" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="23" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="26" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="38" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="38" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="39" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="37" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="37" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="26" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="49" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="21" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="27" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="35" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="37" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="22" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="35" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="22" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="22" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="22" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="38" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="39" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="21" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="38" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="39" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="35" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="36" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="27" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="37" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="35" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="37" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="36" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="35" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="28" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="29" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="30" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="21" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="22" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="38" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="39" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -2412,45 +2497,67 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="22" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="52" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="47" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="53" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="37" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="37" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="22" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="38" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="38" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="39" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="37" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="22" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="41" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="40" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="54" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="34" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="36" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="4" borderId="52" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -2462,185 +2569,117 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="35" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="37" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="35" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="36" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="28" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="29" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="30" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="38" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="39" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="22" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="22" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="36" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="35" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="37" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="37" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="41" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="40" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="54" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="34" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="38" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="38" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="39" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="37" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="52" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="47" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="53" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="35" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="37" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="36" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="38" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="39" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="28" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="29" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="30" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="21" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="22" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="35" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="36" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="27" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -2663,44 +2702,23 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2713,15 +2731,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2730,57 +2739,48 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="47" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="47" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Нейтральный" xfId="2" builtinId="28"/>
@@ -3155,19 +3155,19 @@
     </row>
     <row r="2" spans="1:18" s="47" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A2" s="60" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="F2" s="61" t="s">
         <v>11</v>
       </c>
       <c r="G2" s="60" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="L2" s="61" t="s">
         <v>11</v>
       </c>
       <c r="M2" s="60" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="R2" s="61" t="s">
         <v>11</v>
@@ -3195,34 +3195,34 @@
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A4" s="4" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="B4" s="5"/>
       <c r="C4" s="5"/>
       <c r="D4" s="6"/>
       <c r="E4" s="5"/>
       <c r="F4" s="62" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="H4" s="5"/>
       <c r="I4" s="5"/>
       <c r="J4" s="6"/>
       <c r="K4" s="5"/>
       <c r="L4" s="62" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="M4" s="4" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="N4" s="5"/>
       <c r="O4" s="5"/>
       <c r="P4" s="6"/>
       <c r="Q4" s="5"/>
       <c r="R4" s="62" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.4">
@@ -3230,7 +3230,7 @@
         <v>2</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="D5" s="8"/>
       <c r="E5" s="9" t="s">
@@ -3243,7 +3243,7 @@
         <v>2</v>
       </c>
       <c r="I5" s="8" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="J5" s="8"/>
       <c r="K5" s="9" t="s">
@@ -3256,7 +3256,7 @@
         <v>2</v>
       </c>
       <c r="O5" s="8" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="P5" s="8"/>
       <c r="Q5" s="9" t="s">
@@ -3316,7 +3316,7 @@
       </c>
       <c r="D7" s="13"/>
       <c r="E7" s="14" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="F7" s="15" t="s">
         <v>7</v>
@@ -3329,7 +3329,7 @@
       </c>
       <c r="J7" s="13"/>
       <c r="K7" s="14" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="L7" s="15" t="s">
         <v>7</v>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="P7" s="13"/>
       <c r="Q7" s="14" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="R7" s="15" t="s">
         <v>7</v>
@@ -3350,29 +3350,29 @@
     </row>
     <row r="8" spans="1:18" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A8" s="11" t="s">
-        <v>100</v>
-      </c>
-      <c r="C8" s="137" t="s">
-        <v>105</v>
-      </c>
-      <c r="D8" s="137"/>
-      <c r="E8" s="137"/>
+        <v>97</v>
+      </c>
+      <c r="C8" s="148" t="s">
+        <v>102</v>
+      </c>
+      <c r="D8" s="148"/>
+      <c r="E8" s="148"/>
       <c r="G8" s="11" t="s">
-        <v>100</v>
-      </c>
-      <c r="I8" s="137" t="s">
-        <v>105</v>
-      </c>
-      <c r="J8" s="137"/>
-      <c r="K8" s="137"/>
+        <v>97</v>
+      </c>
+      <c r="I8" s="148" t="s">
+        <v>102</v>
+      </c>
+      <c r="J8" s="148"/>
+      <c r="K8" s="148"/>
       <c r="M8" s="11" t="s">
-        <v>100</v>
-      </c>
-      <c r="O8" s="137" t="s">
-        <v>105</v>
-      </c>
-      <c r="P8" s="137"/>
-      <c r="Q8" s="137"/>
+        <v>97</v>
+      </c>
+      <c r="O8" s="148" t="s">
+        <v>102</v>
+      </c>
+      <c r="P8" s="148"/>
+      <c r="Q8" s="148"/>
     </row>
     <row r="9" spans="1:18" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A9" s="16" t="s">
@@ -3393,24 +3393,24 @@
       <c r="H9" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="I9" s="138" t="s">
+      <c r="I9" s="149" t="s">
         <v>1</v>
       </c>
-      <c r="J9" s="139"/>
-      <c r="K9" s="139"/>
-      <c r="L9" s="140"/>
+      <c r="J9" s="150"/>
+      <c r="K9" s="150"/>
+      <c r="L9" s="151"/>
       <c r="M9" s="16" t="s">
         <v>17</v>
       </c>
       <c r="N9" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="O9" s="138" t="s">
+      <c r="O9" s="149" t="s">
         <v>1</v>
       </c>
-      <c r="P9" s="139"/>
-      <c r="Q9" s="139"/>
-      <c r="R9" s="140"/>
+      <c r="P9" s="150"/>
+      <c r="Q9" s="150"/>
+      <c r="R9" s="151"/>
     </row>
     <row r="10" spans="1:18" ht="37.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="22" t="s">
@@ -3419,136 +3419,136 @@
       <c r="B10" s="23">
         <v>2</v>
       </c>
-      <c r="C10" s="187" t="s">
-        <v>111</v>
-      </c>
-      <c r="D10" s="188"/>
-      <c r="E10" s="188"/>
-      <c r="F10" s="189"/>
+      <c r="C10" s="165" t="s">
+        <v>108</v>
+      </c>
+      <c r="D10" s="166"/>
+      <c r="E10" s="166"/>
+      <c r="F10" s="167"/>
       <c r="G10" s="54" t="s">
         <v>18</v>
       </c>
       <c r="H10" s="23">
         <v>2</v>
       </c>
-      <c r="I10" s="141" t="s">
-        <v>111</v>
-      </c>
-      <c r="J10" s="142"/>
-      <c r="K10" s="142"/>
-      <c r="L10" s="143"/>
+      <c r="I10" s="171" t="s">
+        <v>108</v>
+      </c>
+      <c r="J10" s="172"/>
+      <c r="K10" s="172"/>
+      <c r="L10" s="173"/>
       <c r="M10" s="54" t="s">
         <v>18</v>
       </c>
       <c r="N10" s="23">
         <v>2</v>
       </c>
-      <c r="O10" s="141" t="s">
-        <v>111</v>
-      </c>
-      <c r="P10" s="142"/>
-      <c r="Q10" s="142"/>
-      <c r="R10" s="143"/>
+      <c r="O10" s="171" t="s">
+        <v>108</v>
+      </c>
+      <c r="P10" s="172"/>
+      <c r="Q10" s="172"/>
+      <c r="R10" s="173"/>
     </row>
     <row r="11" spans="1:18" ht="32.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="24"/>
       <c r="B11" s="25">
         <v>3</v>
       </c>
-      <c r="C11" s="190" t="s">
-        <v>112</v>
-      </c>
-      <c r="D11" s="191"/>
-      <c r="E11" s="191"/>
-      <c r="F11" s="192"/>
+      <c r="C11" s="168" t="s">
+        <v>109</v>
+      </c>
+      <c r="D11" s="169"/>
+      <c r="E11" s="169"/>
+      <c r="F11" s="170"/>
       <c r="G11" s="55"/>
       <c r="H11" s="25">
         <v>3</v>
       </c>
-      <c r="I11" s="144" t="s">
-        <v>112</v>
-      </c>
-      <c r="J11" s="145"/>
-      <c r="K11" s="145"/>
-      <c r="L11" s="146"/>
+      <c r="I11" s="127" t="s">
+        <v>109</v>
+      </c>
+      <c r="J11" s="128"/>
+      <c r="K11" s="128"/>
+      <c r="L11" s="129"/>
       <c r="M11" s="55"/>
       <c r="N11" s="25">
         <v>3</v>
       </c>
-      <c r="O11" s="144" t="s">
-        <v>112</v>
-      </c>
-      <c r="P11" s="145"/>
-      <c r="Q11" s="145"/>
-      <c r="R11" s="146"/>
+      <c r="O11" s="127" t="s">
+        <v>109</v>
+      </c>
+      <c r="P11" s="128"/>
+      <c r="Q11" s="128"/>
+      <c r="R11" s="129"/>
     </row>
     <row r="12" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="24"/>
       <c r="B12" s="25">
         <v>4</v>
       </c>
-      <c r="C12" s="88" t="s">
+      <c r="C12" s="105" t="s">
         <v>63</v>
       </c>
-      <c r="D12" s="89"/>
-      <c r="E12" s="89"/>
-      <c r="F12" s="90"/>
+      <c r="D12" s="106"/>
+      <c r="E12" s="106"/>
+      <c r="F12" s="107"/>
       <c r="G12" s="55"/>
       <c r="H12" s="25">
         <v>4</v>
       </c>
-      <c r="I12" s="144" t="s">
-        <v>110</v>
-      </c>
-      <c r="J12" s="198"/>
-      <c r="K12" s="199" t="s">
-        <v>109</v>
-      </c>
-      <c r="L12" s="146"/>
+      <c r="I12" s="127" t="s">
+        <v>107</v>
+      </c>
+      <c r="J12" s="177"/>
+      <c r="K12" s="178" t="s">
+        <v>106</v>
+      </c>
+      <c r="L12" s="129"/>
       <c r="M12" s="55"/>
       <c r="N12" s="25">
         <v>4</v>
       </c>
-      <c r="O12" s="144" t="s">
-        <v>197</v>
-      </c>
-      <c r="P12" s="145"/>
-      <c r="Q12" s="145"/>
-      <c r="R12" s="146"/>
+      <c r="O12" s="127" t="s">
+        <v>193</v>
+      </c>
+      <c r="P12" s="128"/>
+      <c r="Q12" s="128"/>
+      <c r="R12" s="129"/>
     </row>
     <row r="13" spans="1:18" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A13" s="26"/>
       <c r="B13" s="27">
         <v>5</v>
       </c>
-      <c r="C13" s="193" t="s">
-        <v>122</v>
-      </c>
-      <c r="D13" s="194"/>
-      <c r="E13" s="194" t="s">
-        <v>118</v>
-      </c>
-      <c r="F13" s="208"/>
+      <c r="C13" s="130" t="s">
+        <v>119</v>
+      </c>
+      <c r="D13" s="131"/>
+      <c r="E13" s="131" t="s">
+        <v>115</v>
+      </c>
+      <c r="F13" s="132"/>
       <c r="G13" s="56"/>
       <c r="H13" s="27">
         <v>5</v>
       </c>
-      <c r="I13" s="144" t="s">
-        <v>197</v>
-      </c>
-      <c r="J13" s="145"/>
-      <c r="K13" s="145"/>
-      <c r="L13" s="146"/>
+      <c r="I13" s="127" t="s">
+        <v>193</v>
+      </c>
+      <c r="J13" s="128"/>
+      <c r="K13" s="128"/>
+      <c r="L13" s="129"/>
       <c r="M13" s="56"/>
       <c r="N13" s="27">
         <v>5</v>
       </c>
-      <c r="O13" s="91" t="s">
+      <c r="O13" s="87" t="s">
         <v>63</v>
       </c>
-      <c r="P13" s="92"/>
-      <c r="Q13" s="92"/>
-      <c r="R13" s="93"/>
+      <c r="P13" s="88"/>
+      <c r="Q13" s="88"/>
+      <c r="R13" s="89"/>
     </row>
     <row r="14" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="30" t="s">
@@ -3557,158 +3557,158 @@
       <c r="B14" s="31">
         <v>1</v>
       </c>
-      <c r="C14" s="203" t="s">
-        <v>113</v>
-      </c>
-      <c r="D14" s="204"/>
-      <c r="E14" s="204"/>
-      <c r="F14" s="205"/>
+      <c r="C14" s="120" t="s">
+        <v>110</v>
+      </c>
+      <c r="D14" s="121"/>
+      <c r="E14" s="121"/>
+      <c r="F14" s="122"/>
       <c r="G14" s="30" t="s">
         <v>19</v>
       </c>
       <c r="H14" s="31">
         <v>1</v>
       </c>
-      <c r="I14" s="154" t="s">
-        <v>113</v>
-      </c>
-      <c r="J14" s="155"/>
-      <c r="K14" s="155"/>
-      <c r="L14" s="156"/>
+      <c r="I14" s="157" t="s">
+        <v>110</v>
+      </c>
+      <c r="J14" s="158"/>
+      <c r="K14" s="158"/>
+      <c r="L14" s="159"/>
       <c r="M14" s="30" t="s">
         <v>19</v>
       </c>
       <c r="N14" s="31">
         <v>1</v>
       </c>
-      <c r="O14" s="154" t="s">
-        <v>113</v>
-      </c>
-      <c r="P14" s="155"/>
-      <c r="Q14" s="155"/>
-      <c r="R14" s="156"/>
+      <c r="O14" s="157" t="s">
+        <v>110</v>
+      </c>
+      <c r="P14" s="158"/>
+      <c r="Q14" s="158"/>
+      <c r="R14" s="159"/>
     </row>
     <row r="15" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="24"/>
       <c r="B15" s="23">
         <v>2</v>
       </c>
-      <c r="C15" s="88" t="s">
-        <v>114</v>
-      </c>
-      <c r="D15" s="89"/>
-      <c r="E15" s="89"/>
-      <c r="F15" s="90"/>
+      <c r="C15" s="105" t="s">
+        <v>111</v>
+      </c>
+      <c r="D15" s="106"/>
+      <c r="E15" s="106"/>
+      <c r="F15" s="107"/>
       <c r="G15" s="24"/>
       <c r="H15" s="23">
         <v>2</v>
       </c>
-      <c r="I15" s="91" t="s">
-        <v>115</v>
-      </c>
-      <c r="J15" s="92"/>
-      <c r="K15" s="92"/>
-      <c r="L15" s="93"/>
+      <c r="I15" s="87" t="s">
+        <v>112</v>
+      </c>
+      <c r="J15" s="88"/>
+      <c r="K15" s="88"/>
+      <c r="L15" s="89"/>
       <c r="M15" s="24"/>
       <c r="N15" s="23">
         <v>2</v>
       </c>
-      <c r="O15" s="157" t="s">
-        <v>127</v>
-      </c>
-      <c r="P15" s="158"/>
-      <c r="Q15" s="158"/>
-      <c r="R15" s="159"/>
+      <c r="O15" s="203" t="s">
+        <v>124</v>
+      </c>
+      <c r="P15" s="123"/>
+      <c r="Q15" s="123"/>
+      <c r="R15" s="124"/>
     </row>
     <row r="16" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="24"/>
       <c r="B16" s="25">
         <v>3</v>
       </c>
-      <c r="C16" s="144" t="s">
-        <v>116</v>
-      </c>
-      <c r="D16" s="145"/>
-      <c r="E16" s="145"/>
-      <c r="F16" s="146"/>
+      <c r="C16" s="127" t="s">
+        <v>113</v>
+      </c>
+      <c r="D16" s="128"/>
+      <c r="E16" s="128"/>
+      <c r="F16" s="129"/>
       <c r="G16" s="24"/>
       <c r="H16" s="25">
         <v>3</v>
       </c>
-      <c r="I16" s="209" t="s">
+      <c r="I16" s="133" t="s">
         <v>63</v>
       </c>
-      <c r="J16" s="210"/>
-      <c r="K16" s="210"/>
-      <c r="L16" s="211"/>
+      <c r="J16" s="134"/>
+      <c r="K16" s="134"/>
+      <c r="L16" s="135"/>
       <c r="M16" s="24"/>
       <c r="N16" s="25">
         <v>3</v>
       </c>
-      <c r="O16" s="168"/>
-      <c r="P16" s="169"/>
-      <c r="Q16" s="108" t="s">
+      <c r="O16" s="209"/>
+      <c r="P16" s="210"/>
+      <c r="Q16" s="160" t="s">
         <v>43</v>
       </c>
-      <c r="R16" s="109"/>
+      <c r="R16" s="161"/>
     </row>
     <row r="17" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="24"/>
       <c r="B17" s="25">
         <v>4</v>
       </c>
-      <c r="C17" s="195"/>
-      <c r="D17" s="196"/>
-      <c r="E17" s="196"/>
-      <c r="F17" s="197"/>
+      <c r="C17" s="174"/>
+      <c r="D17" s="175"/>
+      <c r="E17" s="175"/>
+      <c r="F17" s="176"/>
       <c r="G17" s="24"/>
       <c r="H17" s="25">
         <v>4</v>
       </c>
-      <c r="I17" s="144" t="s">
+      <c r="I17" s="127" t="s">
         <v>24</v>
       </c>
-      <c r="J17" s="145"/>
-      <c r="K17" s="145"/>
-      <c r="L17" s="146"/>
+      <c r="J17" s="128"/>
+      <c r="K17" s="128"/>
+      <c r="L17" s="129"/>
       <c r="M17" s="24"/>
       <c r="N17" s="25">
         <v>4</v>
       </c>
-      <c r="O17" s="163"/>
-      <c r="P17" s="164"/>
-      <c r="Q17" s="111" t="s">
+      <c r="O17" s="207"/>
+      <c r="P17" s="208"/>
+      <c r="Q17" s="113" t="s">
         <v>43</v>
       </c>
-      <c r="R17" s="112"/>
+      <c r="R17" s="114"/>
     </row>
     <row r="18" spans="1:18" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A18" s="24"/>
       <c r="B18" s="25">
         <v>5</v>
       </c>
-      <c r="C18" s="216" t="s">
+      <c r="C18" s="138" t="s">
         <v>24</v>
       </c>
-      <c r="D18" s="217"/>
-      <c r="E18" s="217"/>
-      <c r="F18" s="218"/>
+      <c r="D18" s="139"/>
+      <c r="E18" s="139"/>
+      <c r="F18" s="140"/>
       <c r="G18" s="24"/>
       <c r="H18" s="25">
         <v>5</v>
       </c>
-      <c r="I18" s="181"/>
-      <c r="J18" s="182"/>
-      <c r="K18" s="182"/>
-      <c r="L18" s="183"/>
+      <c r="I18" s="154"/>
+      <c r="J18" s="155"/>
+      <c r="K18" s="155"/>
+      <c r="L18" s="156"/>
       <c r="M18" s="24"/>
       <c r="N18" s="25">
         <v>5</v>
       </c>
-      <c r="O18" s="160"/>
-      <c r="P18" s="161"/>
-      <c r="Q18" s="161"/>
-      <c r="R18" s="162"/>
+      <c r="O18" s="204"/>
+      <c r="P18" s="205"/>
+      <c r="Q18" s="205"/>
+      <c r="R18" s="206"/>
     </row>
     <row r="19" spans="1:18" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="30" t="s">
@@ -3717,158 +3717,158 @@
       <c r="B19" s="31">
         <v>1</v>
       </c>
-      <c r="C19" s="212"/>
-      <c r="D19" s="213"/>
-      <c r="E19" s="214"/>
-      <c r="F19" s="215"/>
+      <c r="C19" s="90"/>
+      <c r="D19" s="91"/>
+      <c r="E19" s="136"/>
+      <c r="F19" s="137"/>
       <c r="G19" s="30" t="s">
         <v>20</v>
       </c>
       <c r="H19" s="31">
         <v>1</v>
       </c>
-      <c r="I19" s="74"/>
-      <c r="J19" s="75"/>
-      <c r="K19" s="76" t="s">
-        <v>190</v>
-      </c>
-      <c r="L19" s="77"/>
+      <c r="I19" s="228"/>
+      <c r="J19" s="229"/>
+      <c r="K19" s="221" t="s">
+        <v>186</v>
+      </c>
+      <c r="L19" s="230"/>
       <c r="M19" s="30" t="s">
         <v>20</v>
       </c>
       <c r="N19" s="31">
         <v>2</v>
       </c>
-      <c r="O19" s="165" t="s">
+      <c r="O19" s="93" t="s">
         <v>24</v>
       </c>
-      <c r="P19" s="166"/>
-      <c r="Q19" s="166"/>
-      <c r="R19" s="167"/>
+      <c r="P19" s="94"/>
+      <c r="Q19" s="94"/>
+      <c r="R19" s="95"/>
     </row>
     <row r="20" spans="1:18" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="24"/>
       <c r="B20" s="25">
         <v>2</v>
       </c>
-      <c r="C20" s="226" t="s">
-        <v>185</v>
-      </c>
-      <c r="D20" s="227"/>
-      <c r="E20" s="227"/>
-      <c r="F20" s="228"/>
+      <c r="C20" s="74" t="s">
+        <v>181</v>
+      </c>
+      <c r="D20" s="75"/>
+      <c r="E20" s="75"/>
+      <c r="F20" s="76"/>
       <c r="G20" s="24"/>
       <c r="H20" s="25">
         <v>2</v>
       </c>
-      <c r="I20" s="97"/>
-      <c r="J20" s="98"/>
-      <c r="K20" s="111" t="s">
-        <v>190</v>
-      </c>
-      <c r="L20" s="112"/>
+      <c r="I20" s="152"/>
+      <c r="J20" s="153"/>
+      <c r="K20" s="113" t="s">
+        <v>186</v>
+      </c>
+      <c r="L20" s="114"/>
       <c r="M20" s="24"/>
       <c r="N20" s="25">
         <v>4</v>
       </c>
-      <c r="O20" s="88" t="s">
-        <v>110</v>
-      </c>
-      <c r="P20" s="89"/>
-      <c r="Q20" s="111" t="s">
-        <v>120</v>
-      </c>
-      <c r="R20" s="112"/>
+      <c r="O20" s="105" t="s">
+        <v>107</v>
+      </c>
+      <c r="P20" s="106"/>
+      <c r="Q20" s="113" t="s">
+        <v>117</v>
+      </c>
+      <c r="R20" s="114"/>
     </row>
     <row r="21" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="24"/>
       <c r="B21" s="25">
         <v>3</v>
       </c>
-      <c r="C21" s="122" t="s">
-        <v>110</v>
-      </c>
-      <c r="D21" s="123"/>
-      <c r="E21" s="123" t="s">
-        <v>109</v>
-      </c>
-      <c r="F21" s="175"/>
+      <c r="C21" s="111" t="s">
+        <v>107</v>
+      </c>
+      <c r="D21" s="112"/>
+      <c r="E21" s="112" t="s">
+        <v>106</v>
+      </c>
+      <c r="F21" s="142"/>
       <c r="G21" s="24"/>
       <c r="H21" s="25">
         <v>3</v>
       </c>
-      <c r="I21" s="122" t="s">
-        <v>126</v>
-      </c>
-      <c r="J21" s="123"/>
-      <c r="K21" s="219"/>
-      <c r="L21" s="220"/>
+      <c r="I21" s="111" t="s">
+        <v>123</v>
+      </c>
+      <c r="J21" s="112"/>
+      <c r="K21" s="116"/>
+      <c r="L21" s="141"/>
       <c r="M21" s="24"/>
       <c r="N21" s="25">
         <v>5</v>
       </c>
-      <c r="O21" s="122" t="s">
-        <v>126</v>
-      </c>
-      <c r="P21" s="123"/>
-      <c r="Q21" s="124" t="s">
-        <v>119</v>
-      </c>
-      <c r="R21" s="125"/>
+      <c r="O21" s="111" t="s">
+        <v>123</v>
+      </c>
+      <c r="P21" s="112"/>
+      <c r="Q21" s="216" t="s">
+        <v>116</v>
+      </c>
+      <c r="R21" s="217"/>
     </row>
     <row r="22" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="24"/>
       <c r="B22" s="25">
         <v>4</v>
       </c>
-      <c r="C22" s="110" t="s">
+      <c r="C22" s="145" t="s">
         <v>31</v>
       </c>
-      <c r="D22" s="111"/>
-      <c r="E22" s="158"/>
-      <c r="F22" s="159"/>
+      <c r="D22" s="113"/>
+      <c r="E22" s="123"/>
+      <c r="F22" s="124"/>
       <c r="G22" s="24"/>
       <c r="H22" s="25">
         <v>4</v>
       </c>
-      <c r="I22" s="88" t="s">
-        <v>186</v>
-      </c>
-      <c r="J22" s="89"/>
-      <c r="K22" s="89"/>
-      <c r="L22" s="90"/>
+      <c r="I22" s="105" t="s">
+        <v>182</v>
+      </c>
+      <c r="J22" s="106"/>
+      <c r="K22" s="106"/>
+      <c r="L22" s="107"/>
       <c r="M22" s="24"/>
       <c r="N22" s="25">
         <v>6</v>
       </c>
-      <c r="O22" s="126"/>
-      <c r="P22" s="127"/>
-      <c r="Q22" s="128"/>
-      <c r="R22" s="129"/>
+      <c r="O22" s="81"/>
+      <c r="P22" s="218"/>
+      <c r="Q22" s="219"/>
+      <c r="R22" s="83"/>
     </row>
     <row r="23" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A23" s="24"/>
       <c r="B23" s="25">
         <v>5</v>
       </c>
-      <c r="C23" s="193" t="s">
+      <c r="C23" s="130" t="s">
         <v>31</v>
       </c>
-      <c r="D23" s="194"/>
-      <c r="E23" s="206"/>
-      <c r="F23" s="207"/>
+      <c r="D23" s="131"/>
+      <c r="E23" s="125"/>
+      <c r="F23" s="126"/>
       <c r="G23" s="24"/>
       <c r="H23" s="25"/>
-      <c r="I23" s="200"/>
-      <c r="J23" s="201"/>
-      <c r="K23" s="201"/>
-      <c r="L23" s="202"/>
+      <c r="I23" s="179"/>
+      <c r="J23" s="180"/>
+      <c r="K23" s="180"/>
+      <c r="L23" s="181"/>
       <c r="M23" s="24"/>
       <c r="N23" s="25"/>
-      <c r="O23" s="147"/>
-      <c r="P23" s="148"/>
-      <c r="Q23" s="149"/>
-      <c r="R23" s="150"/>
+      <c r="O23" s="185"/>
+      <c r="P23" s="186"/>
+      <c r="Q23" s="198"/>
+      <c r="R23" s="199"/>
     </row>
     <row r="24" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="30" t="s">
@@ -3877,200 +3877,200 @@
       <c r="B24" s="31">
         <v>1</v>
       </c>
-      <c r="C24" s="184" t="s">
-        <v>187</v>
-      </c>
-      <c r="D24" s="185"/>
-      <c r="E24" s="185" t="s">
-        <v>188</v>
-      </c>
-      <c r="F24" s="186"/>
+      <c r="C24" s="162" t="s">
+        <v>183</v>
+      </c>
+      <c r="D24" s="163"/>
+      <c r="E24" s="163" t="s">
+        <v>184</v>
+      </c>
+      <c r="F24" s="164"/>
       <c r="G24" s="30" t="s">
         <v>21</v>
       </c>
       <c r="H24" s="31">
         <v>1</v>
       </c>
-      <c r="I24" s="221"/>
-      <c r="J24" s="222"/>
-      <c r="K24" s="213" t="s">
-        <v>108</v>
-      </c>
-      <c r="L24" s="223"/>
+      <c r="I24" s="143"/>
+      <c r="J24" s="144"/>
+      <c r="K24" s="91" t="s">
+        <v>105</v>
+      </c>
+      <c r="L24" s="92"/>
       <c r="M24" s="30" t="s">
         <v>21</v>
       </c>
       <c r="N24" s="31">
         <v>1</v>
       </c>
-      <c r="O24" s="130"/>
-      <c r="P24" s="76"/>
-      <c r="Q24" s="131"/>
-      <c r="R24" s="132"/>
+      <c r="O24" s="220"/>
+      <c r="P24" s="221"/>
+      <c r="Q24" s="222"/>
+      <c r="R24" s="223"/>
     </row>
     <row r="25" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="24"/>
       <c r="B25" s="25">
         <v>2</v>
       </c>
-      <c r="C25" s="88" t="s">
-        <v>187</v>
-      </c>
-      <c r="D25" s="89"/>
-      <c r="E25" s="89" t="s">
-        <v>188</v>
-      </c>
-      <c r="F25" s="90"/>
+      <c r="C25" s="105" t="s">
+        <v>183</v>
+      </c>
+      <c r="D25" s="106"/>
+      <c r="E25" s="106" t="s">
+        <v>184</v>
+      </c>
+      <c r="F25" s="107"/>
       <c r="G25" s="24"/>
       <c r="H25" s="25">
         <v>2</v>
       </c>
-      <c r="I25" s="88" t="s">
-        <v>124</v>
-      </c>
-      <c r="J25" s="89"/>
-      <c r="K25" s="108" t="s">
+      <c r="I25" s="105" t="s">
+        <v>121</v>
+      </c>
+      <c r="J25" s="106"/>
+      <c r="K25" s="160" t="s">
         <v>43</v>
       </c>
-      <c r="L25" s="109"/>
+      <c r="L25" s="161"/>
       <c r="M25" s="24"/>
       <c r="N25" s="25">
         <v>2</v>
       </c>
-      <c r="O25" s="133"/>
-      <c r="P25" s="134"/>
-      <c r="Q25" s="135"/>
-      <c r="R25" s="136"/>
+      <c r="O25" s="224"/>
+      <c r="P25" s="225"/>
+      <c r="Q25" s="226"/>
+      <c r="R25" s="227"/>
     </row>
     <row r="26" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="24"/>
       <c r="B26" s="25">
         <v>3</v>
       </c>
-      <c r="C26" s="224"/>
-      <c r="D26" s="225"/>
-      <c r="E26" s="89" t="s">
-        <v>125</v>
-      </c>
-      <c r="F26" s="90"/>
+      <c r="C26" s="146"/>
+      <c r="D26" s="147"/>
+      <c r="E26" s="106" t="s">
+        <v>122</v>
+      </c>
+      <c r="F26" s="107"/>
       <c r="G26" s="24"/>
       <c r="H26" s="25">
         <v>3</v>
       </c>
-      <c r="I26" s="88" t="s">
-        <v>189</v>
-      </c>
-      <c r="J26" s="89"/>
-      <c r="K26" s="111" t="s">
+      <c r="I26" s="105" t="s">
+        <v>185</v>
+      </c>
+      <c r="J26" s="106"/>
+      <c r="K26" s="113" t="s">
         <v>43</v>
       </c>
-      <c r="L26" s="112"/>
+      <c r="L26" s="114"/>
       <c r="M26" s="24"/>
       <c r="N26" s="25">
         <v>3</v>
       </c>
-      <c r="O26" s="88" t="s">
-        <v>189</v>
-      </c>
-      <c r="P26" s="89"/>
-      <c r="Q26" s="111"/>
-      <c r="R26" s="112"/>
+      <c r="O26" s="105" t="s">
+        <v>185</v>
+      </c>
+      <c r="P26" s="106"/>
+      <c r="Q26" s="113"/>
+      <c r="R26" s="114"/>
     </row>
     <row r="27" spans="1:18" ht="36" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A27" s="26"/>
       <c r="B27" s="27">
         <v>4</v>
       </c>
-      <c r="C27" s="122" t="s">
-        <v>126</v>
-      </c>
-      <c r="D27" s="123"/>
-      <c r="E27" s="123" t="s">
+      <c r="C27" s="111" t="s">
+        <v>123</v>
+      </c>
+      <c r="D27" s="112"/>
+      <c r="E27" s="112" t="s">
         <v>43</v>
       </c>
-      <c r="F27" s="175"/>
+      <c r="F27" s="142"/>
       <c r="G27" s="26"/>
       <c r="H27" s="27">
         <v>4</v>
       </c>
-      <c r="I27" s="91" t="s">
-        <v>189</v>
-      </c>
-      <c r="J27" s="117"/>
-      <c r="K27" s="118" t="s">
-        <v>125</v>
-      </c>
-      <c r="L27" s="93"/>
+      <c r="I27" s="87" t="s">
+        <v>185</v>
+      </c>
+      <c r="J27" s="188"/>
+      <c r="K27" s="189" t="s">
+        <v>122</v>
+      </c>
+      <c r="L27" s="89"/>
       <c r="M27" s="26"/>
       <c r="N27" s="27">
         <v>4</v>
       </c>
-      <c r="O27" s="115" t="s">
-        <v>192</v>
-      </c>
-      <c r="P27" s="116"/>
-      <c r="Q27" s="108" t="s">
-        <v>195</v>
-      </c>
-      <c r="R27" s="109"/>
+      <c r="O27" s="211" t="s">
+        <v>188</v>
+      </c>
+      <c r="P27" s="212"/>
+      <c r="Q27" s="160" t="s">
+        <v>191</v>
+      </c>
+      <c r="R27" s="161"/>
     </row>
     <row r="28" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A28" s="26"/>
       <c r="B28" s="27">
         <v>5</v>
       </c>
-      <c r="C28" s="238"/>
-      <c r="D28" s="219"/>
-      <c r="E28" s="123" t="s">
+      <c r="C28" s="115"/>
+      <c r="D28" s="116"/>
+      <c r="E28" s="112" t="s">
         <v>43</v>
       </c>
-      <c r="F28" s="175"/>
+      <c r="F28" s="142"/>
       <c r="G28" s="26"/>
       <c r="H28" s="27">
         <v>5</v>
       </c>
-      <c r="I28" s="126"/>
-      <c r="J28" s="170"/>
-      <c r="K28" s="170"/>
-      <c r="L28" s="129"/>
+      <c r="I28" s="81"/>
+      <c r="J28" s="82"/>
+      <c r="K28" s="82"/>
+      <c r="L28" s="83"/>
       <c r="M28" s="26"/>
       <c r="N28" s="27">
         <v>5</v>
       </c>
-      <c r="O28" s="91" t="s">
-        <v>124</v>
-      </c>
-      <c r="P28" s="117"/>
-      <c r="Q28" s="118" t="s">
-        <v>125</v>
-      </c>
-      <c r="R28" s="93"/>
+      <c r="O28" s="87" t="s">
+        <v>121</v>
+      </c>
+      <c r="P28" s="188"/>
+      <c r="Q28" s="189" t="s">
+        <v>122</v>
+      </c>
+      <c r="R28" s="89"/>
     </row>
     <row r="29" spans="1:18" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A29" s="32"/>
       <c r="B29" s="29"/>
-      <c r="C29" s="147"/>
-      <c r="D29" s="148"/>
-      <c r="E29" s="148"/>
-      <c r="F29" s="174"/>
+      <c r="C29" s="185"/>
+      <c r="D29" s="186"/>
+      <c r="E29" s="186"/>
+      <c r="F29" s="187"/>
       <c r="G29" s="32"/>
       <c r="H29" s="29">
         <v>6</v>
       </c>
-      <c r="I29" s="171"/>
-      <c r="J29" s="172"/>
-      <c r="K29" s="172"/>
-      <c r="L29" s="173"/>
+      <c r="I29" s="182"/>
+      <c r="J29" s="183"/>
+      <c r="K29" s="183"/>
+      <c r="L29" s="184"/>
       <c r="M29" s="32"/>
       <c r="N29" s="29">
         <v>6</v>
       </c>
-      <c r="O29" s="151" t="s">
+      <c r="O29" s="200" t="s">
         <v>48</v>
       </c>
-      <c r="P29" s="152"/>
-      <c r="Q29" s="152"/>
-      <c r="R29" s="153"/>
+      <c r="P29" s="201"/>
+      <c r="Q29" s="201"/>
+      <c r="R29" s="202"/>
     </row>
     <row r="30" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A30" s="30" t="s">
@@ -4079,168 +4079,168 @@
       <c r="B30" s="31">
         <v>1</v>
       </c>
-      <c r="C30" s="178"/>
-      <c r="D30" s="179"/>
-      <c r="E30" s="179"/>
-      <c r="F30" s="180"/>
+      <c r="C30" s="192"/>
+      <c r="D30" s="193"/>
+      <c r="E30" s="193"/>
+      <c r="F30" s="194"/>
       <c r="G30" s="30" t="s">
         <v>22</v>
       </c>
       <c r="H30" s="31">
         <v>1</v>
       </c>
-      <c r="I30" s="85" t="s">
+      <c r="I30" s="102" t="s">
         <v>46</v>
       </c>
-      <c r="J30" s="86"/>
-      <c r="K30" s="176" t="s">
-        <v>191</v>
-      </c>
-      <c r="L30" s="177"/>
+      <c r="J30" s="103"/>
+      <c r="K30" s="190" t="s">
+        <v>187</v>
+      </c>
+      <c r="L30" s="191"/>
       <c r="M30" s="30" t="s">
         <v>22</v>
       </c>
       <c r="N30" s="31">
         <v>1</v>
       </c>
-      <c r="O30" s="119" t="s">
-        <v>193</v>
-      </c>
-      <c r="P30" s="120"/>
-      <c r="Q30" s="120"/>
-      <c r="R30" s="121"/>
+      <c r="O30" s="213" t="s">
+        <v>189</v>
+      </c>
+      <c r="P30" s="214"/>
+      <c r="Q30" s="214"/>
+      <c r="R30" s="215"/>
     </row>
     <row r="31" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A31" s="33"/>
       <c r="B31" s="23">
         <v>2</v>
       </c>
-      <c r="C31" s="122" t="s">
-        <v>127</v>
-      </c>
-      <c r="D31" s="123"/>
-      <c r="E31" s="123"/>
-      <c r="F31" s="175"/>
+      <c r="C31" s="111" t="s">
+        <v>124</v>
+      </c>
+      <c r="D31" s="112"/>
+      <c r="E31" s="112"/>
+      <c r="F31" s="142"/>
       <c r="G31" s="33"/>
       <c r="H31" s="23">
         <v>2</v>
       </c>
-      <c r="I31" s="88" t="s">
+      <c r="I31" s="105" t="s">
         <v>47</v>
       </c>
-      <c r="J31" s="89"/>
-      <c r="K31" s="111" t="s">
-        <v>191</v>
-      </c>
-      <c r="L31" s="112"/>
+      <c r="J31" s="106"/>
+      <c r="K31" s="113" t="s">
+        <v>187</v>
+      </c>
+      <c r="L31" s="114"/>
       <c r="M31" s="33"/>
       <c r="N31" s="23">
         <v>2</v>
       </c>
-      <c r="O31" s="110" t="s">
-        <v>194</v>
-      </c>
-      <c r="P31" s="111"/>
-      <c r="Q31" s="111"/>
-      <c r="R31" s="112"/>
+      <c r="O31" s="145" t="s">
+        <v>190</v>
+      </c>
+      <c r="P31" s="113"/>
+      <c r="Q31" s="113"/>
+      <c r="R31" s="114"/>
     </row>
     <row r="32" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A32" s="33"/>
       <c r="B32" s="25">
         <v>3</v>
       </c>
-      <c r="C32" s="110" t="s">
-        <v>123</v>
-      </c>
-      <c r="D32" s="111"/>
-      <c r="E32" s="111" t="s">
+      <c r="C32" s="145" t="s">
         <v>120</v>
       </c>
-      <c r="F32" s="112"/>
+      <c r="D32" s="113"/>
+      <c r="E32" s="113" t="s">
+        <v>117</v>
+      </c>
+      <c r="F32" s="114"/>
       <c r="G32" s="33"/>
       <c r="H32" s="25">
         <v>3</v>
       </c>
-      <c r="I32" s="79" t="s">
-        <v>127</v>
-      </c>
-      <c r="J32" s="80"/>
-      <c r="K32" s="80"/>
-      <c r="L32" s="81"/>
+      <c r="I32" s="117" t="s">
+        <v>124</v>
+      </c>
+      <c r="J32" s="118"/>
+      <c r="K32" s="118"/>
+      <c r="L32" s="119"/>
       <c r="M32" s="33"/>
       <c r="N32" s="25">
         <v>3</v>
       </c>
-      <c r="O32" s="113" t="s">
+      <c r="O32" s="237" t="s">
         <v>47</v>
       </c>
-      <c r="P32" s="114"/>
-      <c r="Q32" s="98" t="s">
-        <v>188</v>
-      </c>
-      <c r="R32" s="99"/>
+      <c r="P32" s="238"/>
+      <c r="Q32" s="153" t="s">
+        <v>184</v>
+      </c>
+      <c r="R32" s="231"/>
     </row>
     <row r="33" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A33" s="33"/>
       <c r="B33" s="25">
         <v>4</v>
       </c>
-      <c r="C33" s="91" t="s">
-        <v>129</v>
-      </c>
-      <c r="D33" s="92"/>
-      <c r="E33" s="92"/>
-      <c r="F33" s="93"/>
+      <c r="C33" s="87" t="s">
+        <v>126</v>
+      </c>
+      <c r="D33" s="88"/>
+      <c r="E33" s="88"/>
+      <c r="F33" s="89"/>
       <c r="G33" s="33"/>
       <c r="H33" s="25">
         <v>4</v>
       </c>
-      <c r="I33" s="106" t="s">
-        <v>128</v>
-      </c>
-      <c r="J33" s="107"/>
-      <c r="K33" s="108" t="s">
-        <v>120</v>
-      </c>
-      <c r="L33" s="109"/>
+      <c r="I33" s="235" t="s">
+        <v>125</v>
+      </c>
+      <c r="J33" s="236"/>
+      <c r="K33" s="160" t="s">
+        <v>117</v>
+      </c>
+      <c r="L33" s="161"/>
       <c r="M33" s="33"/>
       <c r="N33" s="25">
         <v>4</v>
       </c>
-      <c r="O33" s="97" t="s">
+      <c r="O33" s="152" t="s">
         <v>46</v>
       </c>
-      <c r="P33" s="98"/>
-      <c r="Q33" s="98" t="s">
-        <v>188</v>
-      </c>
-      <c r="R33" s="99"/>
+      <c r="P33" s="153"/>
+      <c r="Q33" s="153" t="s">
+        <v>184</v>
+      </c>
+      <c r="R33" s="231"/>
     </row>
     <row r="34" spans="1:18" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A34" s="34"/>
       <c r="B34" s="27">
         <v>5</v>
       </c>
-      <c r="C34" s="126"/>
-      <c r="D34" s="170"/>
-      <c r="E34" s="170"/>
-      <c r="F34" s="129"/>
+      <c r="C34" s="81"/>
+      <c r="D34" s="82"/>
+      <c r="E34" s="82"/>
+      <c r="F34" s="83"/>
       <c r="G34" s="35"/>
       <c r="H34" s="29">
         <v>5</v>
       </c>
-      <c r="I34" s="229"/>
-      <c r="J34" s="230"/>
-      <c r="K34" s="230"/>
-      <c r="L34" s="231"/>
+      <c r="I34" s="78"/>
+      <c r="J34" s="79"/>
+      <c r="K34" s="79"/>
+      <c r="L34" s="80"/>
       <c r="M34" s="35"/>
       <c r="N34" s="29">
         <v>5</v>
       </c>
-      <c r="O34" s="94"/>
-      <c r="P34" s="95"/>
-      <c r="Q34" s="95"/>
-      <c r="R34" s="96"/>
+      <c r="O34" s="99"/>
+      <c r="P34" s="100"/>
+      <c r="Q34" s="100"/>
+      <c r="R34" s="101"/>
     </row>
     <row r="35" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A35" s="42" t="s">
@@ -4249,304 +4249,304 @@
       <c r="B35" s="31">
         <v>1</v>
       </c>
-      <c r="C35" s="165" t="s">
+      <c r="C35" s="93" t="s">
         <v>25</v>
       </c>
-      <c r="D35" s="166"/>
-      <c r="E35" s="166"/>
-      <c r="F35" s="167"/>
+      <c r="D35" s="94"/>
+      <c r="E35" s="94"/>
+      <c r="F35" s="95"/>
       <c r="G35" s="36" t="s">
         <v>23</v>
       </c>
       <c r="H35" s="23">
         <v>2</v>
       </c>
-      <c r="I35" s="212" t="s">
+      <c r="I35" s="90" t="s">
         <v>25</v>
       </c>
-      <c r="J35" s="213"/>
-      <c r="K35" s="213"/>
-      <c r="L35" s="223"/>
+      <c r="J35" s="91"/>
+      <c r="K35" s="91"/>
+      <c r="L35" s="92"/>
       <c r="M35" s="36" t="s">
         <v>23</v>
       </c>
       <c r="N35" s="23">
         <v>3</v>
       </c>
-      <c r="O35" s="100" t="s">
+      <c r="O35" s="232" t="s">
         <v>25</v>
       </c>
-      <c r="P35" s="101"/>
-      <c r="Q35" s="101"/>
-      <c r="R35" s="102"/>
+      <c r="P35" s="233"/>
+      <c r="Q35" s="233"/>
+      <c r="R35" s="234"/>
     </row>
     <row r="36" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A36" s="37"/>
       <c r="B36" s="25">
         <v>3</v>
       </c>
-      <c r="C36" s="91"/>
-      <c r="D36" s="92"/>
-      <c r="E36" s="92"/>
-      <c r="F36" s="93"/>
+      <c r="C36" s="87"/>
+      <c r="D36" s="88"/>
+      <c r="E36" s="88"/>
+      <c r="F36" s="89"/>
       <c r="G36" s="37"/>
       <c r="H36" s="25">
         <v>4</v>
       </c>
-      <c r="I36" s="103" t="s">
+      <c r="I36" s="84" t="s">
         <v>48</v>
       </c>
-      <c r="J36" s="104"/>
-      <c r="K36" s="104"/>
-      <c r="L36" s="105"/>
+      <c r="J36" s="85"/>
+      <c r="K36" s="85"/>
+      <c r="L36" s="86"/>
       <c r="M36" s="37"/>
       <c r="N36" s="25">
         <v>5</v>
       </c>
-      <c r="O36" s="103" t="s">
-        <v>130</v>
-      </c>
-      <c r="P36" s="104"/>
-      <c r="Q36" s="104"/>
-      <c r="R36" s="105"/>
+      <c r="O36" s="84" t="s">
+        <v>127</v>
+      </c>
+      <c r="P36" s="85"/>
+      <c r="Q36" s="85"/>
+      <c r="R36" s="86"/>
     </row>
     <row r="37" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A37" s="37"/>
       <c r="B37" s="25">
         <v>4</v>
       </c>
-      <c r="C37" s="91" t="s">
-        <v>117</v>
-      </c>
-      <c r="D37" s="92"/>
-      <c r="E37" s="92"/>
-      <c r="F37" s="93"/>
+      <c r="C37" s="87" t="s">
+        <v>114</v>
+      </c>
+      <c r="D37" s="88"/>
+      <c r="E37" s="88"/>
+      <c r="F37" s="89"/>
       <c r="G37" s="37"/>
       <c r="H37" s="25">
         <v>5</v>
       </c>
-      <c r="I37" s="232"/>
-      <c r="J37" s="233"/>
-      <c r="K37" s="233"/>
-      <c r="L37" s="234"/>
+      <c r="I37" s="96"/>
+      <c r="J37" s="97"/>
+      <c r="K37" s="97"/>
+      <c r="L37" s="98"/>
       <c r="M37" s="37"/>
       <c r="N37" s="25">
         <v>6</v>
       </c>
-      <c r="O37" s="79"/>
-      <c r="P37" s="80"/>
-      <c r="Q37" s="80"/>
-      <c r="R37" s="81"/>
+      <c r="O37" s="117"/>
+      <c r="P37" s="118"/>
+      <c r="Q37" s="118"/>
+      <c r="R37" s="119"/>
     </row>
     <row r="38" spans="1:18" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A38" s="63"/>
       <c r="B38" s="29">
         <v>5</v>
       </c>
-      <c r="C38" s="235"/>
-      <c r="D38" s="236"/>
-      <c r="E38" s="236"/>
-      <c r="F38" s="237"/>
+      <c r="C38" s="108"/>
+      <c r="D38" s="109"/>
+      <c r="E38" s="109"/>
+      <c r="F38" s="110"/>
       <c r="G38" s="38"/>
       <c r="H38" s="27">
         <v>6</v>
       </c>
-      <c r="I38" s="82"/>
-      <c r="J38" s="83"/>
-      <c r="K38" s="83"/>
-      <c r="L38" s="84"/>
+      <c r="I38" s="195"/>
+      <c r="J38" s="196"/>
+      <c r="K38" s="196"/>
+      <c r="L38" s="197"/>
       <c r="M38" s="38"/>
       <c r="N38" s="27"/>
-      <c r="O38" s="82"/>
-      <c r="P38" s="83"/>
-      <c r="Q38" s="83"/>
-      <c r="R38" s="84"/>
+      <c r="O38" s="195"/>
+      <c r="P38" s="196"/>
+      <c r="Q38" s="196"/>
+      <c r="R38" s="197"/>
     </row>
     <row r="39" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A39" s="50"/>
       <c r="B39" s="31" t="s">
         <v>27</v>
       </c>
-      <c r="C39" s="85" t="s">
+      <c r="C39" s="102" t="s">
         <v>29</v>
       </c>
-      <c r="D39" s="86"/>
-      <c r="E39" s="86"/>
-      <c r="F39" s="87"/>
+      <c r="D39" s="103"/>
+      <c r="E39" s="103"/>
+      <c r="F39" s="104"/>
       <c r="G39" s="50"/>
       <c r="H39" s="31" t="s">
         <v>27</v>
       </c>
-      <c r="I39" s="85" t="s">
+      <c r="I39" s="102" t="s">
         <v>29</v>
       </c>
-      <c r="J39" s="86"/>
-      <c r="K39" s="86"/>
-      <c r="L39" s="87"/>
+      <c r="J39" s="103"/>
+      <c r="K39" s="103"/>
+      <c r="L39" s="104"/>
       <c r="M39" s="50"/>
       <c r="N39" s="31" t="s">
         <v>27</v>
       </c>
-      <c r="O39" s="85" t="s">
+      <c r="O39" s="102" t="s">
         <v>29</v>
       </c>
-      <c r="P39" s="86"/>
-      <c r="Q39" s="86"/>
-      <c r="R39" s="87"/>
+      <c r="P39" s="103"/>
+      <c r="Q39" s="103"/>
+      <c r="R39" s="104"/>
     </row>
     <row r="40" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A40" s="37"/>
       <c r="B40" s="25" t="s">
         <v>27</v>
       </c>
-      <c r="C40" s="88" t="s">
+      <c r="C40" s="105" t="s">
         <v>61</v>
       </c>
-      <c r="D40" s="89"/>
-      <c r="E40" s="89"/>
-      <c r="F40" s="90"/>
+      <c r="D40" s="106"/>
+      <c r="E40" s="106"/>
+      <c r="F40" s="107"/>
       <c r="G40" s="37"/>
       <c r="H40" s="25" t="s">
         <v>27</v>
       </c>
-      <c r="I40" s="88" t="s">
+      <c r="I40" s="105" t="s">
         <v>61</v>
       </c>
-      <c r="J40" s="89"/>
-      <c r="K40" s="89"/>
-      <c r="L40" s="90"/>
+      <c r="J40" s="106"/>
+      <c r="K40" s="106"/>
+      <c r="L40" s="107"/>
       <c r="M40" s="37"/>
       <c r="N40" s="25" t="s">
         <v>27</v>
       </c>
-      <c r="O40" s="88" t="s">
+      <c r="O40" s="105" t="s">
         <v>61</v>
       </c>
-      <c r="P40" s="89"/>
-      <c r="Q40" s="89"/>
-      <c r="R40" s="90"/>
+      <c r="P40" s="106"/>
+      <c r="Q40" s="106"/>
+      <c r="R40" s="107"/>
     </row>
     <row r="41" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A41" s="38"/>
       <c r="B41" s="27" t="s">
         <v>27</v>
       </c>
-      <c r="C41" s="91" t="s">
-        <v>107</v>
-      </c>
-      <c r="D41" s="92"/>
-      <c r="E41" s="92"/>
-      <c r="F41" s="93"/>
+      <c r="C41" s="87" t="s">
+        <v>104</v>
+      </c>
+      <c r="D41" s="88"/>
+      <c r="E41" s="88"/>
+      <c r="F41" s="89"/>
       <c r="G41" s="38"/>
       <c r="H41" s="27" t="s">
         <v>27</v>
       </c>
-      <c r="I41" s="91" t="s">
-        <v>107</v>
-      </c>
-      <c r="J41" s="92"/>
-      <c r="K41" s="92"/>
-      <c r="L41" s="93"/>
+      <c r="I41" s="87" t="s">
+        <v>104</v>
+      </c>
+      <c r="J41" s="88"/>
+      <c r="K41" s="88"/>
+      <c r="L41" s="89"/>
       <c r="M41" s="38"/>
       <c r="N41" s="27" t="s">
         <v>27</v>
       </c>
-      <c r="O41" s="91" t="s">
-        <v>107</v>
-      </c>
-      <c r="P41" s="92"/>
-      <c r="Q41" s="92"/>
-      <c r="R41" s="93"/>
+      <c r="O41" s="87" t="s">
+        <v>104</v>
+      </c>
+      <c r="P41" s="88"/>
+      <c r="Q41" s="88"/>
+      <c r="R41" s="89"/>
     </row>
     <row r="42" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A42" s="38"/>
       <c r="B42" s="27" t="s">
         <v>27</v>
       </c>
-      <c r="C42" s="91" t="s">
+      <c r="C42" s="87" t="s">
         <v>62</v>
       </c>
-      <c r="D42" s="92"/>
-      <c r="E42" s="92"/>
-      <c r="F42" s="93"/>
+      <c r="D42" s="88"/>
+      <c r="E42" s="88"/>
+      <c r="F42" s="89"/>
       <c r="G42" s="38"/>
       <c r="H42" s="27" t="s">
         <v>27</v>
       </c>
-      <c r="I42" s="91" t="s">
+      <c r="I42" s="87" t="s">
         <v>62</v>
       </c>
-      <c r="J42" s="92"/>
-      <c r="K42" s="92"/>
-      <c r="L42" s="93"/>
+      <c r="J42" s="88"/>
+      <c r="K42" s="88"/>
+      <c r="L42" s="89"/>
       <c r="M42" s="38"/>
       <c r="N42" s="27" t="s">
         <v>27</v>
       </c>
-      <c r="O42" s="91" t="s">
+      <c r="O42" s="87" t="s">
         <v>62</v>
       </c>
-      <c r="P42" s="92"/>
-      <c r="Q42" s="92"/>
-      <c r="R42" s="93"/>
+      <c r="P42" s="88"/>
+      <c r="Q42" s="88"/>
+      <c r="R42" s="89"/>
     </row>
     <row r="43" spans="1:18" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A43" s="39"/>
       <c r="B43" s="51" t="s">
         <v>27</v>
       </c>
-      <c r="C43" s="94" t="s">
+      <c r="C43" s="99" t="s">
         <v>30</v>
       </c>
-      <c r="D43" s="95"/>
-      <c r="E43" s="95"/>
-      <c r="F43" s="96"/>
+      <c r="D43" s="100"/>
+      <c r="E43" s="100"/>
+      <c r="F43" s="101"/>
       <c r="G43" s="39"/>
       <c r="H43" s="51" t="s">
         <v>27</v>
       </c>
-      <c r="I43" s="94" t="s">
+      <c r="I43" s="99" t="s">
         <v>30</v>
       </c>
-      <c r="J43" s="95"/>
-      <c r="K43" s="95"/>
-      <c r="L43" s="96"/>
+      <c r="J43" s="100"/>
+      <c r="K43" s="100"/>
+      <c r="L43" s="101"/>
       <c r="M43" s="39"/>
       <c r="N43" s="51" t="s">
         <v>27</v>
       </c>
-      <c r="O43" s="94" t="s">
+      <c r="O43" s="99" t="s">
         <v>30</v>
       </c>
-      <c r="P43" s="95"/>
-      <c r="Q43" s="95"/>
-      <c r="R43" s="96"/>
+      <c r="P43" s="100"/>
+      <c r="Q43" s="100"/>
+      <c r="R43" s="101"/>
     </row>
     <row r="44" spans="1:18" ht="48.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A44" s="78" t="s">
-        <v>121</v>
-      </c>
-      <c r="B44" s="78"/>
-      <c r="C44" s="78"/>
-      <c r="D44" s="78"/>
-      <c r="E44" s="78"/>
-      <c r="F44" s="78"/>
-      <c r="G44" s="78" t="s">
-        <v>121</v>
-      </c>
-      <c r="H44" s="78"/>
-      <c r="I44" s="78"/>
-      <c r="J44" s="78"/>
-      <c r="K44" s="78"/>
-      <c r="L44" s="78"/>
-      <c r="M44" s="78" t="s">
-        <v>121</v>
-      </c>
-      <c r="N44" s="78"/>
-      <c r="O44" s="78"/>
-      <c r="P44" s="78"/>
-      <c r="Q44" s="78"/>
-      <c r="R44" s="78"/>
+      <c r="A44" s="77" t="s">
+        <v>118</v>
+      </c>
+      <c r="B44" s="77"/>
+      <c r="C44" s="77"/>
+      <c r="D44" s="77"/>
+      <c r="E44" s="77"/>
+      <c r="F44" s="77"/>
+      <c r="G44" s="77" t="s">
+        <v>118</v>
+      </c>
+      <c r="H44" s="77"/>
+      <c r="I44" s="77"/>
+      <c r="J44" s="77"/>
+      <c r="K44" s="77"/>
+      <c r="L44" s="77"/>
+      <c r="M44" s="77" t="s">
+        <v>118</v>
+      </c>
+      <c r="N44" s="77"/>
+      <c r="O44" s="77"/>
+      <c r="P44" s="77"/>
+      <c r="Q44" s="77"/>
+      <c r="R44" s="77"/>
     </row>
     <row r="45" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A45" s="2" t="s">
@@ -4590,14 +4590,136 @@
     </row>
     <row r="49" spans="7:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.45"/>
     <row r="50" spans="7:11" x14ac:dyDescent="0.4">
-      <c r="G50" s="78"/>
-      <c r="H50" s="78"/>
-      <c r="I50" s="78"/>
-      <c r="J50" s="78"/>
-      <c r="K50" s="78"/>
+      <c r="G50" s="77"/>
+      <c r="H50" s="77"/>
+      <c r="I50" s="77"/>
+      <c r="J50" s="77"/>
+      <c r="K50" s="77"/>
     </row>
   </sheetData>
   <mergeCells count="146">
+    <mergeCell ref="I19:J19"/>
+    <mergeCell ref="K19:L19"/>
+    <mergeCell ref="G50:K50"/>
+    <mergeCell ref="O37:R37"/>
+    <mergeCell ref="O38:R38"/>
+    <mergeCell ref="O39:R39"/>
+    <mergeCell ref="O40:R40"/>
+    <mergeCell ref="O42:R42"/>
+    <mergeCell ref="O43:R43"/>
+    <mergeCell ref="M44:R44"/>
+    <mergeCell ref="O33:P33"/>
+    <mergeCell ref="Q33:R33"/>
+    <mergeCell ref="O34:R34"/>
+    <mergeCell ref="O35:R35"/>
+    <mergeCell ref="O36:R36"/>
+    <mergeCell ref="O41:R41"/>
+    <mergeCell ref="I41:L41"/>
+    <mergeCell ref="I33:J33"/>
+    <mergeCell ref="K33:L33"/>
+    <mergeCell ref="O31:R31"/>
+    <mergeCell ref="O32:P32"/>
+    <mergeCell ref="Q32:R32"/>
+    <mergeCell ref="O26:P26"/>
+    <mergeCell ref="Q26:R26"/>
+    <mergeCell ref="O27:P27"/>
+    <mergeCell ref="Q27:R27"/>
+    <mergeCell ref="O28:P28"/>
+    <mergeCell ref="Q28:R28"/>
+    <mergeCell ref="O30:R30"/>
+    <mergeCell ref="Q16:R16"/>
+    <mergeCell ref="O21:P21"/>
+    <mergeCell ref="Q21:R21"/>
+    <mergeCell ref="O22:P22"/>
+    <mergeCell ref="Q22:R22"/>
+    <mergeCell ref="O24:P24"/>
+    <mergeCell ref="Q24:R24"/>
+    <mergeCell ref="O25:P25"/>
+    <mergeCell ref="Q25:R25"/>
+    <mergeCell ref="C32:D32"/>
+    <mergeCell ref="E32:F32"/>
+    <mergeCell ref="O8:Q8"/>
+    <mergeCell ref="O9:R9"/>
+    <mergeCell ref="O10:R10"/>
+    <mergeCell ref="O11:R11"/>
+    <mergeCell ref="O12:R12"/>
+    <mergeCell ref="O13:R13"/>
+    <mergeCell ref="I43:L43"/>
+    <mergeCell ref="I38:L38"/>
+    <mergeCell ref="I39:L39"/>
+    <mergeCell ref="O23:P23"/>
+    <mergeCell ref="Q23:R23"/>
+    <mergeCell ref="O29:R29"/>
+    <mergeCell ref="O14:R14"/>
+    <mergeCell ref="O15:R15"/>
+    <mergeCell ref="O18:R18"/>
+    <mergeCell ref="O20:P20"/>
+    <mergeCell ref="Q20:R20"/>
+    <mergeCell ref="O17:P17"/>
+    <mergeCell ref="Q17:R17"/>
+    <mergeCell ref="O19:R19"/>
+    <mergeCell ref="O16:P16"/>
+    <mergeCell ref="I31:J31"/>
+    <mergeCell ref="K31:L31"/>
+    <mergeCell ref="I28:L28"/>
+    <mergeCell ref="I29:L29"/>
+    <mergeCell ref="C29:F29"/>
+    <mergeCell ref="I27:J27"/>
+    <mergeCell ref="K27:L27"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="K30:L30"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="C31:F31"/>
+    <mergeCell ref="C30:F30"/>
+    <mergeCell ref="I30:J30"/>
+    <mergeCell ref="C8:E8"/>
+    <mergeCell ref="I8:K8"/>
+    <mergeCell ref="I9:L9"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="I20:J20"/>
+    <mergeCell ref="K20:L20"/>
+    <mergeCell ref="I18:L18"/>
+    <mergeCell ref="I14:L14"/>
+    <mergeCell ref="I15:L15"/>
+    <mergeCell ref="K25:L25"/>
+    <mergeCell ref="I25:J25"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="C10:F10"/>
+    <mergeCell ref="C11:F11"/>
+    <mergeCell ref="I10:L10"/>
+    <mergeCell ref="C15:F15"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="C17:F17"/>
+    <mergeCell ref="I11:L11"/>
+    <mergeCell ref="I12:J12"/>
+    <mergeCell ref="K12:L12"/>
+    <mergeCell ref="I23:L23"/>
+    <mergeCell ref="C12:F12"/>
+    <mergeCell ref="C14:F14"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="I26:J26"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="I13:L13"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="E13:F13"/>
+    <mergeCell ref="I22:L22"/>
+    <mergeCell ref="C16:F16"/>
+    <mergeCell ref="I17:L17"/>
+    <mergeCell ref="I16:L16"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="C18:F18"/>
+    <mergeCell ref="K21:L21"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="I24:J24"/>
+    <mergeCell ref="K24:L24"/>
+    <mergeCell ref="I21:J21"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="C26:D26"/>
     <mergeCell ref="C20:F20"/>
     <mergeCell ref="A44:F44"/>
     <mergeCell ref="G44:L44"/>
@@ -4622,128 +4744,6 @@
     <mergeCell ref="K26:L26"/>
     <mergeCell ref="C28:D28"/>
     <mergeCell ref="I32:L32"/>
-    <mergeCell ref="C12:F12"/>
-    <mergeCell ref="C14:F14"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="I26:J26"/>
-    <mergeCell ref="E26:F26"/>
-    <mergeCell ref="I13:L13"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="E13:F13"/>
-    <mergeCell ref="I22:L22"/>
-    <mergeCell ref="C16:F16"/>
-    <mergeCell ref="I17:L17"/>
-    <mergeCell ref="I16:L16"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="C18:F18"/>
-    <mergeCell ref="K21:L21"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="I24:J24"/>
-    <mergeCell ref="K24:L24"/>
-    <mergeCell ref="I21:J21"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="C8:E8"/>
-    <mergeCell ref="I8:K8"/>
-    <mergeCell ref="I9:L9"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="I20:J20"/>
-    <mergeCell ref="K20:L20"/>
-    <mergeCell ref="I18:L18"/>
-    <mergeCell ref="I14:L14"/>
-    <mergeCell ref="I15:L15"/>
-    <mergeCell ref="K25:L25"/>
-    <mergeCell ref="I25:J25"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="C10:F10"/>
-    <mergeCell ref="C11:F11"/>
-    <mergeCell ref="I10:L10"/>
-    <mergeCell ref="C15:F15"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="C17:F17"/>
-    <mergeCell ref="I11:L11"/>
-    <mergeCell ref="I12:J12"/>
-    <mergeCell ref="K12:L12"/>
-    <mergeCell ref="I23:L23"/>
-    <mergeCell ref="K31:L31"/>
-    <mergeCell ref="I28:L28"/>
-    <mergeCell ref="I29:L29"/>
-    <mergeCell ref="C29:F29"/>
-    <mergeCell ref="I27:J27"/>
-    <mergeCell ref="K27:L27"/>
-    <mergeCell ref="E27:F27"/>
-    <mergeCell ref="K30:L30"/>
-    <mergeCell ref="E28:F28"/>
-    <mergeCell ref="C31:F31"/>
-    <mergeCell ref="C30:F30"/>
-    <mergeCell ref="I30:J30"/>
-    <mergeCell ref="C32:D32"/>
-    <mergeCell ref="E32:F32"/>
-    <mergeCell ref="O8:Q8"/>
-    <mergeCell ref="O9:R9"/>
-    <mergeCell ref="O10:R10"/>
-    <mergeCell ref="O11:R11"/>
-    <mergeCell ref="O12:R12"/>
-    <mergeCell ref="O13:R13"/>
-    <mergeCell ref="I43:L43"/>
-    <mergeCell ref="I38:L38"/>
-    <mergeCell ref="I39:L39"/>
-    <mergeCell ref="O23:P23"/>
-    <mergeCell ref="Q23:R23"/>
-    <mergeCell ref="O29:R29"/>
-    <mergeCell ref="O14:R14"/>
-    <mergeCell ref="O15:R15"/>
-    <mergeCell ref="O18:R18"/>
-    <mergeCell ref="O20:P20"/>
-    <mergeCell ref="Q20:R20"/>
-    <mergeCell ref="O17:P17"/>
-    <mergeCell ref="Q17:R17"/>
-    <mergeCell ref="O19:R19"/>
-    <mergeCell ref="O16:P16"/>
-    <mergeCell ref="I31:J31"/>
-    <mergeCell ref="O27:P27"/>
-    <mergeCell ref="Q27:R27"/>
-    <mergeCell ref="O28:P28"/>
-    <mergeCell ref="Q28:R28"/>
-    <mergeCell ref="O30:R30"/>
-    <mergeCell ref="Q16:R16"/>
-    <mergeCell ref="O21:P21"/>
-    <mergeCell ref="Q21:R21"/>
-    <mergeCell ref="O22:P22"/>
-    <mergeCell ref="Q22:R22"/>
-    <mergeCell ref="O24:P24"/>
-    <mergeCell ref="Q24:R24"/>
-    <mergeCell ref="O25:P25"/>
-    <mergeCell ref="Q25:R25"/>
-    <mergeCell ref="I19:J19"/>
-    <mergeCell ref="K19:L19"/>
-    <mergeCell ref="G50:K50"/>
-    <mergeCell ref="O37:R37"/>
-    <mergeCell ref="O38:R38"/>
-    <mergeCell ref="O39:R39"/>
-    <mergeCell ref="O40:R40"/>
-    <mergeCell ref="O42:R42"/>
-    <mergeCell ref="O43:R43"/>
-    <mergeCell ref="M44:R44"/>
-    <mergeCell ref="O33:P33"/>
-    <mergeCell ref="Q33:R33"/>
-    <mergeCell ref="O34:R34"/>
-    <mergeCell ref="O35:R35"/>
-    <mergeCell ref="O36:R36"/>
-    <mergeCell ref="O41:R41"/>
-    <mergeCell ref="I41:L41"/>
-    <mergeCell ref="I33:J33"/>
-    <mergeCell ref="K33:L33"/>
-    <mergeCell ref="O31:R31"/>
-    <mergeCell ref="O32:P32"/>
-    <mergeCell ref="Q32:R32"/>
-    <mergeCell ref="O26:P26"/>
-    <mergeCell ref="Q26:R26"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E5 K5 Q5">
@@ -4830,7 +4830,7 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="B2" s="47"/>
       <c r="C2" s="47"/>
@@ -4840,7 +4840,7 @@
         <v>11</v>
       </c>
       <c r="G2" s="60" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="H2" s="47"/>
       <c r="I2" s="47"/>
@@ -4874,24 +4874,24 @@
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A4" s="4" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="B4" s="5"/>
       <c r="C4" s="5"/>
       <c r="D4" s="6"/>
       <c r="E4" s="5"/>
       <c r="F4" s="62" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="H4" s="5"/>
       <c r="I4" s="5"/>
       <c r="J4" s="6"/>
       <c r="K4" s="5"/>
       <c r="L4" s="62" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.4">
@@ -4899,7 +4899,7 @@
         <v>2</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="D5" s="8"/>
       <c r="E5" s="9" t="s">
@@ -4912,7 +4912,7 @@
         <v>2</v>
       </c>
       <c r="I5" s="8" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="J5" s="8"/>
       <c r="K5" s="9" t="s">
@@ -4980,21 +4980,21 @@
     </row>
     <row r="8" spans="1:12" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A8" s="11" t="s">
-        <v>100</v>
-      </c>
-      <c r="C8" s="137" t="s">
-        <v>105</v>
-      </c>
-      <c r="D8" s="137"/>
-      <c r="E8" s="137"/>
+        <v>97</v>
+      </c>
+      <c r="C8" s="148" t="s">
+        <v>102</v>
+      </c>
+      <c r="D8" s="148"/>
+      <c r="E8" s="148"/>
       <c r="G8" s="11" t="s">
-        <v>100</v>
-      </c>
-      <c r="I8" s="137" t="s">
-        <v>105</v>
-      </c>
-      <c r="J8" s="137"/>
-      <c r="K8" s="137"/>
+        <v>97</v>
+      </c>
+      <c r="I8" s="148" t="s">
+        <v>102</v>
+      </c>
+      <c r="J8" s="148"/>
+      <c r="K8" s="148"/>
     </row>
     <row r="9" spans="1:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A9" s="16" t="s">
@@ -5015,12 +5015,12 @@
       <c r="H9" s="68" t="s">
         <v>0</v>
       </c>
-      <c r="I9" s="138" t="s">
+      <c r="I9" s="149" t="s">
         <v>1</v>
       </c>
-      <c r="J9" s="139"/>
-      <c r="K9" s="139"/>
-      <c r="L9" s="140"/>
+      <c r="J9" s="150"/>
+      <c r="K9" s="150"/>
+      <c r="L9" s="151"/>
     </row>
     <row r="10" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="22" t="s">
@@ -5029,108 +5029,108 @@
       <c r="B10" s="31" t="s">
         <v>64</v>
       </c>
-      <c r="C10" s="276" t="s">
+      <c r="C10" s="249" t="s">
         <v>65</v>
       </c>
-      <c r="D10" s="277"/>
-      <c r="E10" s="277"/>
-      <c r="F10" s="278"/>
+      <c r="D10" s="250"/>
+      <c r="E10" s="250"/>
+      <c r="F10" s="251"/>
       <c r="G10" s="69" t="s">
         <v>18</v>
       </c>
       <c r="H10" s="71" t="s">
         <v>64</v>
       </c>
-      <c r="I10" s="276" t="s">
+      <c r="I10" s="249" t="s">
         <v>65</v>
       </c>
-      <c r="J10" s="277"/>
-      <c r="K10" s="277"/>
-      <c r="L10" s="278"/>
+      <c r="J10" s="250"/>
+      <c r="K10" s="250"/>
+      <c r="L10" s="251"/>
     </row>
     <row r="11" spans="1:12" ht="32.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="24"/>
       <c r="B11" s="25">
         <v>4</v>
       </c>
-      <c r="C11" s="254" t="s">
+      <c r="C11" s="264" t="s">
         <v>68</v>
       </c>
-      <c r="D11" s="255"/>
-      <c r="E11" s="256"/>
-      <c r="F11" s="257"/>
+      <c r="D11" s="328"/>
+      <c r="E11" s="340"/>
+      <c r="F11" s="341"/>
       <c r="G11" s="70"/>
       <c r="H11" s="72">
         <v>4</v>
       </c>
-      <c r="I11" s="264" t="s">
-        <v>141</v>
-      </c>
-      <c r="J11" s="265"/>
-      <c r="K11" s="265"/>
-      <c r="L11" s="268"/>
+      <c r="I11" s="296" t="s">
+        <v>138</v>
+      </c>
+      <c r="J11" s="297"/>
+      <c r="K11" s="297"/>
+      <c r="L11" s="338"/>
     </row>
     <row r="12" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="24"/>
       <c r="B12" s="25">
         <v>5</v>
       </c>
-      <c r="C12" s="254"/>
-      <c r="D12" s="255"/>
-      <c r="E12" s="135"/>
-      <c r="F12" s="136"/>
+      <c r="C12" s="264"/>
+      <c r="D12" s="328"/>
+      <c r="E12" s="226"/>
+      <c r="F12" s="227"/>
       <c r="G12" s="70"/>
       <c r="H12" s="72">
         <v>5</v>
       </c>
-      <c r="I12" s="254"/>
-      <c r="J12" s="272"/>
-      <c r="K12" s="272"/>
-      <c r="L12" s="273"/>
+      <c r="I12" s="264"/>
+      <c r="J12" s="265"/>
+      <c r="K12" s="265"/>
+      <c r="L12" s="266"/>
     </row>
     <row r="13" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="24"/>
       <c r="B13" s="25">
         <v>6</v>
       </c>
-      <c r="C13" s="262"/>
-      <c r="D13" s="263"/>
-      <c r="E13" s="108" t="s">
+      <c r="C13" s="346"/>
+      <c r="D13" s="347"/>
+      <c r="E13" s="160" t="s">
         <v>35</v>
       </c>
-      <c r="F13" s="109"/>
+      <c r="F13" s="161"/>
       <c r="G13" s="70"/>
       <c r="H13" s="72">
         <v>6</v>
       </c>
-      <c r="I13" s="264" t="s">
-        <v>198</v>
-      </c>
-      <c r="J13" s="265"/>
-      <c r="K13" s="266"/>
-      <c r="L13" s="267"/>
+      <c r="I13" s="296" t="s">
+        <v>194</v>
+      </c>
+      <c r="J13" s="297"/>
+      <c r="K13" s="348"/>
+      <c r="L13" s="349"/>
     </row>
     <row r="14" spans="1:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A14" s="24"/>
       <c r="B14" s="25">
         <v>7</v>
       </c>
-      <c r="C14" s="281"/>
-      <c r="D14" s="282"/>
-      <c r="E14" s="283" t="s">
+      <c r="C14" s="329"/>
+      <c r="D14" s="330"/>
+      <c r="E14" s="331" t="s">
         <v>35</v>
       </c>
-      <c r="F14" s="284"/>
+      <c r="F14" s="332"/>
       <c r="G14" s="70"/>
       <c r="H14" s="73">
         <v>7</v>
       </c>
-      <c r="I14" s="269" t="s">
-        <v>198</v>
-      </c>
-      <c r="J14" s="270"/>
-      <c r="K14" s="270"/>
-      <c r="L14" s="271"/>
+      <c r="I14" s="350" t="s">
+        <v>194</v>
+      </c>
+      <c r="J14" s="351"/>
+      <c r="K14" s="351"/>
+      <c r="L14" s="352"/>
     </row>
     <row r="15" spans="1:12" ht="31.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="30" t="s">
@@ -5139,118 +5139,118 @@
       <c r="B15" s="31">
         <v>1</v>
       </c>
-      <c r="C15" s="309"/>
-      <c r="D15" s="131"/>
-      <c r="E15" s="260" t="s">
-        <v>196</v>
-      </c>
-      <c r="F15" s="261"/>
+      <c r="C15" s="280"/>
+      <c r="D15" s="222"/>
+      <c r="E15" s="344" t="s">
+        <v>192</v>
+      </c>
+      <c r="F15" s="345"/>
       <c r="G15" s="30" t="s">
         <v>19</v>
       </c>
       <c r="H15" s="23">
         <v>1</v>
       </c>
-      <c r="I15" s="279"/>
-      <c r="J15" s="185"/>
-      <c r="K15" s="258" t="s">
+      <c r="I15" s="327"/>
+      <c r="J15" s="163"/>
+      <c r="K15" s="342" t="s">
         <v>66</v>
       </c>
-      <c r="L15" s="259"/>
+      <c r="L15" s="343"/>
     </row>
     <row r="16" spans="1:12" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="24"/>
       <c r="B16" s="23">
         <v>2</v>
       </c>
-      <c r="C16" s="244" t="s">
-        <v>153</v>
-      </c>
-      <c r="D16" s="245"/>
-      <c r="E16" s="245" t="s">
-        <v>196</v>
-      </c>
-      <c r="F16" s="246"/>
+      <c r="C16" s="281" t="s">
+        <v>149</v>
+      </c>
+      <c r="D16" s="282"/>
+      <c r="E16" s="282" t="s">
+        <v>192</v>
+      </c>
+      <c r="F16" s="320"/>
       <c r="G16" s="24"/>
       <c r="H16" s="23">
         <v>2</v>
       </c>
-      <c r="I16" s="244" t="s">
+      <c r="I16" s="281" t="s">
         <v>67</v>
       </c>
-      <c r="J16" s="111"/>
-      <c r="K16" s="289" t="s">
-        <v>150</v>
-      </c>
-      <c r="L16" s="159"/>
+      <c r="J16" s="113"/>
+      <c r="K16" s="337" t="s">
+        <v>146</v>
+      </c>
+      <c r="L16" s="124"/>
     </row>
     <row r="17" spans="1:12" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="24"/>
       <c r="B17" s="25">
         <v>3</v>
       </c>
-      <c r="C17" s="274"/>
-      <c r="D17" s="308"/>
-      <c r="E17" s="249" t="s">
-        <v>154</v>
-      </c>
-      <c r="F17" s="250"/>
+      <c r="C17" s="276"/>
+      <c r="D17" s="277"/>
+      <c r="E17" s="278" t="s">
+        <v>150</v>
+      </c>
+      <c r="F17" s="279"/>
       <c r="G17" s="24"/>
       <c r="H17" s="25">
         <v>3</v>
       </c>
-      <c r="I17" s="247" t="s">
+      <c r="I17" s="321" t="s">
         <v>68</v>
       </c>
-      <c r="J17" s="248"/>
-      <c r="K17" s="249" t="s">
-        <v>196</v>
-      </c>
-      <c r="L17" s="250"/>
+      <c r="J17" s="355"/>
+      <c r="K17" s="278" t="s">
+        <v>192</v>
+      </c>
+      <c r="L17" s="279"/>
     </row>
     <row r="18" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="24"/>
       <c r="B18" s="25">
         <v>4</v>
       </c>
-      <c r="C18" s="244" t="s">
-        <v>125</v>
-      </c>
-      <c r="D18" s="245"/>
-      <c r="E18" s="308"/>
-      <c r="F18" s="310"/>
+      <c r="C18" s="281" t="s">
+        <v>122</v>
+      </c>
+      <c r="D18" s="282"/>
+      <c r="E18" s="277"/>
+      <c r="F18" s="283"/>
       <c r="G18" s="24"/>
       <c r="H18" s="25">
         <v>4</v>
       </c>
-      <c r="I18" s="280" t="s">
-        <v>153</v>
-      </c>
-      <c r="J18" s="116"/>
-      <c r="K18" s="249" t="s">
-        <v>196</v>
-      </c>
-      <c r="L18" s="250"/>
+      <c r="I18" s="262" t="s">
+        <v>149</v>
+      </c>
+      <c r="J18" s="212"/>
+      <c r="K18" s="278" t="s">
+        <v>192</v>
+      </c>
+      <c r="L18" s="279"/>
     </row>
     <row r="19" spans="1:12" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A19" s="26"/>
       <c r="B19" s="27">
         <v>5</v>
       </c>
-      <c r="C19" s="293"/>
-      <c r="D19" s="294"/>
-      <c r="E19" s="295"/>
-      <c r="F19" s="296"/>
+      <c r="C19" s="313"/>
+      <c r="D19" s="314"/>
+      <c r="E19" s="315"/>
+      <c r="F19" s="316"/>
       <c r="G19" s="26"/>
       <c r="H19" s="27">
         <v>5</v>
       </c>
-      <c r="I19" s="110" t="s">
-        <v>136</v>
-      </c>
-      <c r="J19" s="111"/>
-      <c r="K19" s="111"/>
-      <c r="L19" s="112"/>
+      <c r="I19" s="145" t="s">
+        <v>133</v>
+      </c>
+      <c r="J19" s="113"/>
+      <c r="K19" s="113"/>
+      <c r="L19" s="114"/>
     </row>
     <row r="20" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="30" t="s">
@@ -5259,116 +5259,116 @@
       <c r="B20" s="31">
         <v>1</v>
       </c>
-      <c r="C20" s="184" t="s">
-        <v>69</v>
-      </c>
-      <c r="D20" s="185"/>
-      <c r="E20" s="185"/>
-      <c r="F20" s="186"/>
+      <c r="C20" s="162" t="s">
+        <v>202</v>
+      </c>
+      <c r="D20" s="163"/>
+      <c r="E20" s="163"/>
+      <c r="F20" s="164"/>
       <c r="G20" s="30" t="s">
         <v>20</v>
       </c>
       <c r="H20" s="31">
         <v>1</v>
       </c>
-      <c r="I20" s="287"/>
-      <c r="J20" s="288"/>
-      <c r="K20" s="285"/>
-      <c r="L20" s="286"/>
+      <c r="I20" s="335"/>
+      <c r="J20" s="336"/>
+      <c r="K20" s="333"/>
+      <c r="L20" s="334"/>
     </row>
     <row r="21" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="24"/>
       <c r="B21" s="25">
         <v>2</v>
       </c>
-      <c r="C21" s="239" t="s">
-        <v>70</v>
-      </c>
-      <c r="D21" s="240"/>
-      <c r="E21" s="241" t="s">
-        <v>142</v>
-      </c>
-      <c r="F21" s="242"/>
+      <c r="C21" s="353" t="s">
+        <v>203</v>
+      </c>
+      <c r="D21" s="300"/>
+      <c r="E21" s="354" t="s">
+        <v>204</v>
+      </c>
+      <c r="F21" s="301"/>
       <c r="G21" s="24"/>
       <c r="H21" s="25">
         <v>2</v>
       </c>
-      <c r="I21" s="244" t="s">
-        <v>72</v>
-      </c>
-      <c r="J21" s="111"/>
-      <c r="K21" s="251"/>
-      <c r="L21" s="252"/>
+      <c r="I21" s="281" t="s">
+        <v>69</v>
+      </c>
+      <c r="J21" s="113"/>
+      <c r="K21" s="356"/>
+      <c r="L21" s="357"/>
     </row>
     <row r="22" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="24"/>
       <c r="B22" s="25">
         <v>3</v>
       </c>
-      <c r="C22" s="244" t="s">
+      <c r="C22" s="281" t="s">
         <v>38</v>
       </c>
-      <c r="D22" s="111"/>
-      <c r="E22" s="245" t="s">
-        <v>71</v>
-      </c>
-      <c r="F22" s="112"/>
+      <c r="D22" s="113"/>
+      <c r="E22" s="282" t="s">
+        <v>205</v>
+      </c>
+      <c r="F22" s="114"/>
       <c r="G22" s="24"/>
       <c r="H22" s="25">
         <v>3</v>
       </c>
-      <c r="I22" s="290" t="s">
-        <v>72</v>
-      </c>
-      <c r="J22" s="158"/>
-      <c r="K22" s="249" t="s">
-        <v>125</v>
-      </c>
-      <c r="L22" s="90"/>
+      <c r="I22" s="339" t="s">
+        <v>69</v>
+      </c>
+      <c r="J22" s="123"/>
+      <c r="K22" s="278" t="s">
+        <v>122</v>
+      </c>
+      <c r="L22" s="107"/>
     </row>
     <row r="23" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="24"/>
       <c r="B23" s="25">
         <v>4</v>
       </c>
-      <c r="C23" s="115" t="s">
-        <v>138</v>
-      </c>
-      <c r="D23" s="253"/>
-      <c r="E23" s="253"/>
-      <c r="F23" s="109"/>
+      <c r="C23" s="211" t="s">
+        <v>135</v>
+      </c>
+      <c r="D23" s="272"/>
+      <c r="E23" s="272"/>
+      <c r="F23" s="161"/>
       <c r="G23" s="24"/>
       <c r="H23" s="25">
         <v>4</v>
       </c>
-      <c r="I23" s="115" t="s">
-        <v>138</v>
-      </c>
-      <c r="J23" s="253"/>
-      <c r="K23" s="253"/>
-      <c r="L23" s="109"/>
+      <c r="I23" s="211" t="s">
+        <v>135</v>
+      </c>
+      <c r="J23" s="272"/>
+      <c r="K23" s="272"/>
+      <c r="L23" s="161"/>
     </row>
     <row r="24" spans="1:12" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A24" s="32"/>
       <c r="B24" s="29">
         <v>5</v>
       </c>
-      <c r="C24" s="334" t="s">
-        <v>148</v>
-      </c>
-      <c r="D24" s="152"/>
-      <c r="E24" s="152"/>
-      <c r="F24" s="153"/>
+      <c r="C24" s="239" t="s">
+        <v>144</v>
+      </c>
+      <c r="D24" s="201"/>
+      <c r="E24" s="201"/>
+      <c r="F24" s="202"/>
       <c r="G24" s="32"/>
       <c r="H24" s="29">
         <v>5</v>
       </c>
-      <c r="I24" s="343" t="s">
-        <v>139</v>
-      </c>
-      <c r="J24" s="230"/>
-      <c r="K24" s="230"/>
-      <c r="L24" s="231"/>
+      <c r="I24" s="252" t="s">
+        <v>136</v>
+      </c>
+      <c r="J24" s="79"/>
+      <c r="K24" s="79"/>
+      <c r="L24" s="80"/>
     </row>
     <row r="25" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="30" t="s">
@@ -5377,104 +5377,104 @@
       <c r="B25" s="31" t="s">
         <v>64</v>
       </c>
-      <c r="C25" s="276" t="s">
+      <c r="C25" s="249" t="s">
         <v>65</v>
       </c>
-      <c r="D25" s="277"/>
-      <c r="E25" s="277"/>
-      <c r="F25" s="278"/>
+      <c r="D25" s="250"/>
+      <c r="E25" s="250"/>
+      <c r="F25" s="251"/>
       <c r="G25" s="30" t="s">
         <v>21</v>
       </c>
       <c r="H25" s="31" t="s">
         <v>64</v>
       </c>
-      <c r="I25" s="276" t="s">
+      <c r="I25" s="249" t="s">
         <v>65</v>
       </c>
-      <c r="J25" s="277"/>
-      <c r="K25" s="277"/>
-      <c r="L25" s="278"/>
+      <c r="J25" s="250"/>
+      <c r="K25" s="250"/>
+      <c r="L25" s="251"/>
     </row>
     <row r="26" spans="1:12" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="24"/>
       <c r="B26" s="25">
         <v>4</v>
       </c>
-      <c r="C26" s="247" t="s">
-        <v>72</v>
-      </c>
-      <c r="D26" s="301"/>
-      <c r="E26" s="302" t="s">
-        <v>152</v>
-      </c>
-      <c r="F26" s="125"/>
+      <c r="C26" s="321" t="s">
+        <v>69</v>
+      </c>
+      <c r="D26" s="322"/>
+      <c r="E26" s="323" t="s">
+        <v>148</v>
+      </c>
+      <c r="F26" s="217"/>
       <c r="G26" s="24"/>
       <c r="H26" s="25">
         <v>4</v>
       </c>
-      <c r="I26" s="347"/>
-      <c r="J26" s="348"/>
-      <c r="K26" s="348"/>
-      <c r="L26" s="349"/>
+      <c r="I26" s="256"/>
+      <c r="J26" s="257"/>
+      <c r="K26" s="257"/>
+      <c r="L26" s="258"/>
     </row>
     <row r="27" spans="1:12" ht="33.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A27" s="24"/>
       <c r="B27" s="25">
         <v>5</v>
       </c>
-      <c r="C27" s="244" t="s">
-        <v>72</v>
-      </c>
-      <c r="D27" s="111"/>
-      <c r="E27" s="245" t="s">
-        <v>133</v>
-      </c>
-      <c r="F27" s="112"/>
+      <c r="C27" s="281" t="s">
+        <v>69</v>
+      </c>
+      <c r="D27" s="113"/>
+      <c r="E27" s="282" t="s">
+        <v>130</v>
+      </c>
+      <c r="F27" s="114"/>
       <c r="G27" s="24"/>
       <c r="H27" s="25">
         <v>5</v>
       </c>
-      <c r="I27" s="350"/>
-      <c r="J27" s="351"/>
-      <c r="K27" s="351"/>
-      <c r="L27" s="352"/>
+      <c r="I27" s="259"/>
+      <c r="J27" s="260"/>
+      <c r="K27" s="260"/>
+      <c r="L27" s="261"/>
     </row>
     <row r="28" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A28" s="26"/>
       <c r="B28" s="27">
         <v>6</v>
       </c>
-      <c r="C28" s="243" t="s">
-        <v>135</v>
-      </c>
-      <c r="D28" s="240"/>
-      <c r="E28" s="240"/>
-      <c r="F28" s="242"/>
+      <c r="C28" s="299" t="s">
+        <v>132</v>
+      </c>
+      <c r="D28" s="300"/>
+      <c r="E28" s="300"/>
+      <c r="F28" s="301"/>
       <c r="G28" s="26"/>
       <c r="H28" s="25">
         <v>6</v>
       </c>
-      <c r="I28" s="243" t="s">
-        <v>135</v>
-      </c>
-      <c r="J28" s="240"/>
-      <c r="K28" s="240"/>
-      <c r="L28" s="242"/>
+      <c r="I28" s="299" t="s">
+        <v>132</v>
+      </c>
+      <c r="J28" s="300"/>
+      <c r="K28" s="300"/>
+      <c r="L28" s="301"/>
     </row>
     <row r="29" spans="1:12" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A29" s="32"/>
       <c r="B29" s="29"/>
-      <c r="C29" s="324"/>
-      <c r="D29" s="325"/>
-      <c r="E29" s="325"/>
-      <c r="F29" s="326"/>
+      <c r="C29" s="302"/>
+      <c r="D29" s="303"/>
+      <c r="E29" s="303"/>
+      <c r="F29" s="304"/>
       <c r="G29" s="32"/>
       <c r="H29" s="25"/>
-      <c r="I29" s="327"/>
-      <c r="J29" s="328"/>
-      <c r="K29" s="328"/>
-      <c r="L29" s="329"/>
+      <c r="I29" s="242"/>
+      <c r="J29" s="305"/>
+      <c r="K29" s="305"/>
+      <c r="L29" s="306"/>
     </row>
     <row r="30" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A30" s="22" t="s">
@@ -5483,138 +5483,138 @@
       <c r="B30" s="23">
         <v>1</v>
       </c>
-      <c r="C30" s="306" t="s">
+      <c r="C30" s="324" t="s">
         <v>32</v>
       </c>
-      <c r="D30" s="307"/>
-      <c r="E30" s="332" t="s">
+      <c r="D30" s="325"/>
+      <c r="E30" s="309" t="s">
         <v>36</v>
       </c>
-      <c r="F30" s="333"/>
+      <c r="F30" s="310"/>
       <c r="G30" s="30" t="s">
         <v>22</v>
       </c>
       <c r="H30" s="31">
         <v>1</v>
       </c>
-      <c r="I30" s="340"/>
-      <c r="J30" s="341"/>
-      <c r="K30" s="341"/>
-      <c r="L30" s="342"/>
+      <c r="I30" s="246"/>
+      <c r="J30" s="247"/>
+      <c r="K30" s="247"/>
+      <c r="L30" s="248"/>
     </row>
     <row r="31" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A31" s="33"/>
       <c r="B31" s="23">
         <v>2</v>
       </c>
-      <c r="C31" s="330"/>
-      <c r="D31" s="331"/>
-      <c r="E31" s="353" t="s">
+      <c r="C31" s="307"/>
+      <c r="D31" s="308"/>
+      <c r="E31" s="267" t="s">
         <v>37</v>
       </c>
-      <c r="F31" s="354"/>
+      <c r="F31" s="268"/>
       <c r="G31" s="33"/>
       <c r="H31" s="23">
         <v>2</v>
       </c>
-      <c r="I31" s="297" t="s">
+      <c r="I31" s="298" t="s">
         <v>37</v>
       </c>
-      <c r="J31" s="298"/>
-      <c r="K31" s="245" t="s">
-        <v>151</v>
-      </c>
-      <c r="L31" s="112"/>
+      <c r="J31" s="317"/>
+      <c r="K31" s="282" t="s">
+        <v>147</v>
+      </c>
+      <c r="L31" s="114"/>
     </row>
     <row r="32" spans="1:12" ht="32.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A32" s="33"/>
       <c r="B32" s="25">
         <v>3</v>
       </c>
-      <c r="C32" s="244" t="s">
-        <v>140</v>
-      </c>
-      <c r="D32" s="245"/>
-      <c r="E32" s="245"/>
-      <c r="F32" s="246"/>
+      <c r="C32" s="281" t="s">
+        <v>137</v>
+      </c>
+      <c r="D32" s="282"/>
+      <c r="E32" s="282"/>
+      <c r="F32" s="320"/>
       <c r="G32" s="33"/>
       <c r="H32" s="25">
         <v>3</v>
       </c>
-      <c r="I32" s="297" t="s">
+      <c r="I32" s="298" t="s">
         <v>39</v>
       </c>
-      <c r="J32" s="117"/>
-      <c r="K32" s="323" t="s">
-        <v>132</v>
-      </c>
-      <c r="L32" s="109"/>
+      <c r="J32" s="188"/>
+      <c r="K32" s="263" t="s">
+        <v>129</v>
+      </c>
+      <c r="L32" s="161"/>
     </row>
     <row r="33" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A33" s="33"/>
       <c r="B33" s="25">
         <v>4</v>
       </c>
-      <c r="C33" s="115" t="s">
-        <v>137</v>
-      </c>
-      <c r="D33" s="253"/>
-      <c r="E33" s="253"/>
-      <c r="F33" s="109"/>
+      <c r="C33" s="211" t="s">
+        <v>134</v>
+      </c>
+      <c r="D33" s="272"/>
+      <c r="E33" s="272"/>
+      <c r="F33" s="161"/>
       <c r="G33" s="33"/>
       <c r="H33" s="25">
         <v>4</v>
       </c>
-      <c r="I33" s="115" t="s">
-        <v>137</v>
-      </c>
-      <c r="J33" s="253"/>
-      <c r="K33" s="253"/>
-      <c r="L33" s="109"/>
+      <c r="I33" s="211" t="s">
+        <v>134</v>
+      </c>
+      <c r="J33" s="272"/>
+      <c r="K33" s="272"/>
+      <c r="L33" s="161"/>
     </row>
     <row r="34" spans="1:12" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A34" s="34"/>
       <c r="B34" s="27">
         <v>6</v>
       </c>
-      <c r="C34" s="244" t="s">
+      <c r="C34" s="281" t="s">
         <v>34</v>
       </c>
-      <c r="D34" s="245"/>
-      <c r="E34" s="299"/>
-      <c r="F34" s="300"/>
+      <c r="D34" s="282"/>
+      <c r="E34" s="318"/>
+      <c r="F34" s="319"/>
       <c r="G34" s="34"/>
       <c r="H34" s="27">
         <v>5</v>
       </c>
-      <c r="I34" s="355" t="s">
-        <v>149</v>
-      </c>
-      <c r="J34" s="356"/>
-      <c r="K34" s="356"/>
-      <c r="L34" s="357"/>
+      <c r="I34" s="269" t="s">
+        <v>145</v>
+      </c>
+      <c r="J34" s="270"/>
+      <c r="K34" s="270"/>
+      <c r="L34" s="271"/>
     </row>
     <row r="35" spans="1:12" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A35" s="35"/>
       <c r="B35" s="29">
         <v>7</v>
       </c>
-      <c r="C35" s="319" t="s">
+      <c r="C35" s="292" t="s">
         <v>34</v>
       </c>
-      <c r="D35" s="320"/>
-      <c r="E35" s="321"/>
-      <c r="F35" s="322"/>
+      <c r="D35" s="293"/>
+      <c r="E35" s="294"/>
+      <c r="F35" s="295"/>
       <c r="G35" s="35"/>
       <c r="H35" s="29">
         <v>6</v>
       </c>
-      <c r="I35" s="316" t="s">
+      <c r="I35" s="289" t="s">
         <v>32</v>
       </c>
-      <c r="J35" s="201"/>
-      <c r="K35" s="318"/>
-      <c r="L35" s="202"/>
+      <c r="J35" s="180"/>
+      <c r="K35" s="291"/>
+      <c r="L35" s="181"/>
     </row>
     <row r="36" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A36" s="42" t="s">
@@ -5623,186 +5623,186 @@
       <c r="B36" s="31">
         <v>1</v>
       </c>
-      <c r="C36" s="344" t="s">
+      <c r="C36" s="253" t="s">
         <v>32</v>
       </c>
-      <c r="D36" s="345"/>
-      <c r="E36" s="345"/>
-      <c r="F36" s="346"/>
+      <c r="D36" s="254"/>
+      <c r="E36" s="254"/>
+      <c r="F36" s="255"/>
       <c r="G36" s="42" t="s">
         <v>23</v>
       </c>
       <c r="H36" s="31">
         <v>1</v>
       </c>
-      <c r="I36" s="317" t="s">
-        <v>144</v>
-      </c>
-      <c r="J36" s="120"/>
-      <c r="K36" s="315" t="s">
+      <c r="I36" s="290" t="s">
+        <v>140</v>
+      </c>
+      <c r="J36" s="214"/>
+      <c r="K36" s="288" t="s">
         <v>36</v>
       </c>
-      <c r="L36" s="156"/>
+      <c r="L36" s="159"/>
     </row>
     <row r="37" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A37" s="37"/>
       <c r="B37" s="25">
         <v>2</v>
       </c>
-      <c r="C37" s="254" t="s">
+      <c r="C37" s="264" t="s">
         <v>32</v>
       </c>
-      <c r="D37" s="272"/>
-      <c r="E37" s="272"/>
-      <c r="F37" s="273"/>
+      <c r="D37" s="265"/>
+      <c r="E37" s="265"/>
+      <c r="F37" s="266"/>
       <c r="G37" s="37"/>
       <c r="H37" s="25">
         <v>2</v>
       </c>
-      <c r="I37" s="297" t="s">
-        <v>145</v>
-      </c>
-      <c r="J37" s="298"/>
-      <c r="K37" s="311" t="s">
-        <v>146</v>
-      </c>
-      <c r="L37" s="175"/>
+      <c r="I37" s="298" t="s">
+        <v>141</v>
+      </c>
+      <c r="J37" s="317"/>
+      <c r="K37" s="284" t="s">
+        <v>142</v>
+      </c>
+      <c r="L37" s="142"/>
     </row>
     <row r="38" spans="1:12" ht="31.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A38" s="37"/>
       <c r="B38" s="25">
         <v>3</v>
       </c>
-      <c r="C38" s="264"/>
-      <c r="D38" s="265"/>
-      <c r="E38" s="265" t="s">
+      <c r="C38" s="296"/>
+      <c r="D38" s="297"/>
+      <c r="E38" s="297" t="s">
         <v>66</v>
       </c>
-      <c r="F38" s="268"/>
+      <c r="F38" s="338"/>
       <c r="G38" s="37"/>
       <c r="H38" s="25">
         <v>3</v>
       </c>
-      <c r="I38" s="274"/>
-      <c r="J38" s="134"/>
-      <c r="K38" s="265" t="s">
-        <v>147</v>
-      </c>
-      <c r="L38" s="192"/>
+      <c r="I38" s="276"/>
+      <c r="J38" s="225"/>
+      <c r="K38" s="297" t="s">
+        <v>143</v>
+      </c>
+      <c r="L38" s="170"/>
     </row>
     <row r="39" spans="1:12" ht="32.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A39" s="37"/>
       <c r="B39" s="25">
         <v>4</v>
       </c>
-      <c r="C39" s="280" t="s">
+      <c r="C39" s="262" t="s">
         <v>67</v>
       </c>
-      <c r="D39" s="116"/>
-      <c r="E39" s="323" t="s">
-        <v>164</v>
-      </c>
-      <c r="F39" s="109"/>
+      <c r="D39" s="212"/>
+      <c r="E39" s="263" t="s">
+        <v>160</v>
+      </c>
+      <c r="F39" s="161"/>
       <c r="G39" s="37"/>
       <c r="H39" s="25">
         <v>4</v>
       </c>
-      <c r="I39" s="274" t="s">
+      <c r="I39" s="276" t="s">
         <v>32</v>
       </c>
-      <c r="J39" s="134"/>
-      <c r="K39" s="275" t="s">
-        <v>143</v>
-      </c>
-      <c r="L39" s="93"/>
+      <c r="J39" s="225"/>
+      <c r="K39" s="326" t="s">
+        <v>139</v>
+      </c>
+      <c r="L39" s="89"/>
     </row>
     <row r="40" spans="1:12" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A40" s="63"/>
       <c r="B40" s="29">
         <v>5</v>
       </c>
-      <c r="C40" s="334" t="s">
-        <v>134</v>
-      </c>
-      <c r="D40" s="335"/>
-      <c r="E40" s="335"/>
-      <c r="F40" s="336"/>
+      <c r="C40" s="239" t="s">
+        <v>131</v>
+      </c>
+      <c r="D40" s="240"/>
+      <c r="E40" s="240"/>
+      <c r="F40" s="241"/>
       <c r="G40" s="63"/>
       <c r="H40" s="29">
         <v>5</v>
       </c>
-      <c r="I40" s="327"/>
-      <c r="J40" s="337"/>
-      <c r="K40" s="338" t="s">
-        <v>143</v>
-      </c>
-      <c r="L40" s="339"/>
+      <c r="I40" s="242"/>
+      <c r="J40" s="243"/>
+      <c r="K40" s="244" t="s">
+        <v>139</v>
+      </c>
+      <c r="L40" s="245"/>
     </row>
     <row r="41" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A41" s="64"/>
       <c r="B41" s="65" t="s">
         <v>27</v>
       </c>
-      <c r="C41" s="312" t="s">
-        <v>131</v>
-      </c>
-      <c r="D41" s="313"/>
-      <c r="E41" s="313"/>
-      <c r="F41" s="314"/>
+      <c r="C41" s="285" t="s">
+        <v>128</v>
+      </c>
+      <c r="D41" s="286"/>
+      <c r="E41" s="286"/>
+      <c r="F41" s="287"/>
       <c r="G41" s="64"/>
       <c r="H41" s="65" t="s">
         <v>27</v>
       </c>
-      <c r="I41" s="312" t="s">
-        <v>131</v>
-      </c>
-      <c r="J41" s="313"/>
-      <c r="K41" s="313"/>
-      <c r="L41" s="314"/>
+      <c r="I41" s="285" t="s">
+        <v>128</v>
+      </c>
+      <c r="J41" s="286"/>
+      <c r="K41" s="286"/>
+      <c r="L41" s="287"/>
     </row>
     <row r="42" spans="1:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A42" s="39"/>
       <c r="B42" s="57" t="s">
         <v>27</v>
       </c>
-      <c r="C42" s="303" t="s">
+      <c r="C42" s="273" t="s">
         <v>33</v>
       </c>
-      <c r="D42" s="304"/>
-      <c r="E42" s="304"/>
-      <c r="F42" s="305"/>
+      <c r="D42" s="274"/>
+      <c r="E42" s="274"/>
+      <c r="F42" s="275"/>
       <c r="G42" s="39"/>
       <c r="H42" s="57" t="s">
         <v>27</v>
       </c>
-      <c r="I42" s="303" t="s">
+      <c r="I42" s="273" t="s">
         <v>33</v>
       </c>
-      <c r="J42" s="304"/>
-      <c r="K42" s="304"/>
-      <c r="L42" s="305"/>
+      <c r="J42" s="274"/>
+      <c r="K42" s="274"/>
+      <c r="L42" s="275"/>
     </row>
     <row r="43" spans="1:12" ht="31.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A43" s="291" t="s">
+      <c r="A43" s="311" t="s">
         <v>49</v>
       </c>
-      <c r="B43" s="291"/>
-      <c r="C43" s="292" t="s">
-        <v>155</v>
-      </c>
-      <c r="D43" s="292"/>
-      <c r="E43" s="292"/>
-      <c r="F43" s="292"/>
-      <c r="G43" s="291" t="s">
+      <c r="B43" s="311"/>
+      <c r="C43" s="312" t="s">
+        <v>151</v>
+      </c>
+      <c r="D43" s="312"/>
+      <c r="E43" s="312"/>
+      <c r="F43" s="312"/>
+      <c r="G43" s="311" t="s">
         <v>49</v>
       </c>
-      <c r="H43" s="291"/>
-      <c r="I43" s="292" t="s">
-        <v>155</v>
-      </c>
-      <c r="J43" s="292"/>
-      <c r="K43" s="292"/>
-      <c r="L43" s="292"/>
+      <c r="H43" s="311"/>
+      <c r="I43" s="312" t="s">
+        <v>151</v>
+      </c>
+      <c r="J43" s="312"/>
+      <c r="K43" s="312"/>
+      <c r="L43" s="312"/>
     </row>
     <row r="44" spans="1:12" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A44" s="2" t="s">
@@ -5834,22 +5834,76 @@
     </row>
   </sheetData>
   <mergeCells count="110">
-    <mergeCell ref="C40:F40"/>
-    <mergeCell ref="I40:J40"/>
-    <mergeCell ref="K40:L40"/>
-    <mergeCell ref="I30:L30"/>
-    <mergeCell ref="I25:L25"/>
-    <mergeCell ref="I24:L24"/>
-    <mergeCell ref="C36:F36"/>
-    <mergeCell ref="I26:L26"/>
-    <mergeCell ref="I27:L27"/>
-    <mergeCell ref="C39:D39"/>
-    <mergeCell ref="E39:F39"/>
-    <mergeCell ref="C37:F37"/>
-    <mergeCell ref="E31:F31"/>
-    <mergeCell ref="C24:F24"/>
-    <mergeCell ref="I34:L34"/>
-    <mergeCell ref="C33:F33"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="I28:L28"/>
+    <mergeCell ref="I19:L19"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="I17:J17"/>
+    <mergeCell ref="K17:L17"/>
+    <mergeCell ref="K21:L21"/>
+    <mergeCell ref="C23:F23"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="K15:L15"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="E13:F13"/>
+    <mergeCell ref="I13:J13"/>
+    <mergeCell ref="K13:L13"/>
+    <mergeCell ref="I11:L11"/>
+    <mergeCell ref="I14:J14"/>
+    <mergeCell ref="K14:L14"/>
+    <mergeCell ref="I12:L12"/>
+    <mergeCell ref="C8:E8"/>
+    <mergeCell ref="I8:K8"/>
+    <mergeCell ref="I39:J39"/>
+    <mergeCell ref="K39:L39"/>
+    <mergeCell ref="C25:F25"/>
+    <mergeCell ref="I15:J15"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="I18:J18"/>
+    <mergeCell ref="E12:F12"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="E14:F14"/>
+    <mergeCell ref="K18:L18"/>
+    <mergeCell ref="K20:L20"/>
+    <mergeCell ref="I21:J21"/>
+    <mergeCell ref="I20:J20"/>
+    <mergeCell ref="I23:L23"/>
+    <mergeCell ref="I16:J16"/>
+    <mergeCell ref="K16:L16"/>
+    <mergeCell ref="E38:F38"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="I22:J22"/>
+    <mergeCell ref="I9:L9"/>
+    <mergeCell ref="C10:F10"/>
+    <mergeCell ref="I10:L10"/>
+    <mergeCell ref="A43:B43"/>
+    <mergeCell ref="C43:F43"/>
+    <mergeCell ref="G43:H43"/>
+    <mergeCell ref="I43:L43"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="I33:L33"/>
+    <mergeCell ref="I31:J31"/>
+    <mergeCell ref="K31:L31"/>
+    <mergeCell ref="I38:J38"/>
+    <mergeCell ref="K38:L38"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="E34:F34"/>
+    <mergeCell ref="I37:J37"/>
+    <mergeCell ref="C32:F32"/>
+    <mergeCell ref="K22:L22"/>
+    <mergeCell ref="C34:D34"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="I42:L42"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
     <mergeCell ref="C42:F42"/>
     <mergeCell ref="C17:D17"/>
     <mergeCell ref="E17:F17"/>
@@ -5874,76 +5928,22 @@
     <mergeCell ref="I29:L29"/>
     <mergeCell ref="C31:D31"/>
     <mergeCell ref="E30:F30"/>
-    <mergeCell ref="A43:B43"/>
-    <mergeCell ref="C43:F43"/>
-    <mergeCell ref="G43:H43"/>
-    <mergeCell ref="I43:L43"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="I33:L33"/>
-    <mergeCell ref="I31:J31"/>
-    <mergeCell ref="K31:L31"/>
-    <mergeCell ref="I38:J38"/>
-    <mergeCell ref="K38:L38"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="E34:F34"/>
-    <mergeCell ref="I37:J37"/>
-    <mergeCell ref="C32:F32"/>
-    <mergeCell ref="K22:L22"/>
-    <mergeCell ref="C34:D34"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="E26:F26"/>
-    <mergeCell ref="I42:L42"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="C8:E8"/>
-    <mergeCell ref="I8:K8"/>
-    <mergeCell ref="I39:J39"/>
-    <mergeCell ref="K39:L39"/>
-    <mergeCell ref="C25:F25"/>
-    <mergeCell ref="I15:J15"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="I18:J18"/>
-    <mergeCell ref="E12:F12"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="E14:F14"/>
-    <mergeCell ref="K18:L18"/>
-    <mergeCell ref="K20:L20"/>
-    <mergeCell ref="I21:J21"/>
-    <mergeCell ref="I20:J20"/>
-    <mergeCell ref="I23:L23"/>
-    <mergeCell ref="I16:J16"/>
-    <mergeCell ref="K16:L16"/>
-    <mergeCell ref="E38:F38"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="I22:J22"/>
-    <mergeCell ref="I9:L9"/>
-    <mergeCell ref="C10:F10"/>
-    <mergeCell ref="I10:L10"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="E11:F11"/>
-    <mergeCell ref="K15:L15"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="E13:F13"/>
-    <mergeCell ref="I13:J13"/>
-    <mergeCell ref="K13:L13"/>
-    <mergeCell ref="I11:L11"/>
-    <mergeCell ref="I14:J14"/>
-    <mergeCell ref="K14:L14"/>
-    <mergeCell ref="I12:L12"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="I28:L28"/>
-    <mergeCell ref="I19:L19"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="I17:J17"/>
-    <mergeCell ref="K17:L17"/>
-    <mergeCell ref="K21:L21"/>
-    <mergeCell ref="C23:F23"/>
+    <mergeCell ref="C40:F40"/>
+    <mergeCell ref="I40:J40"/>
+    <mergeCell ref="K40:L40"/>
+    <mergeCell ref="I30:L30"/>
+    <mergeCell ref="I25:L25"/>
+    <mergeCell ref="I24:L24"/>
+    <mergeCell ref="C36:F36"/>
+    <mergeCell ref="I26:L26"/>
+    <mergeCell ref="I27:L27"/>
+    <mergeCell ref="C39:D39"/>
+    <mergeCell ref="E39:F39"/>
+    <mergeCell ref="C37:F37"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="C24:F24"/>
+    <mergeCell ref="I34:L34"/>
+    <mergeCell ref="C33:F33"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation allowBlank="1" showDropDown="1" showInputMessage="1" showErrorMessage="1" sqref="C6 I6"/>
@@ -6023,7 +6023,7 @@
     </row>
     <row r="2" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="60" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="B2" s="47"/>
       <c r="C2" s="47"/>
@@ -6033,7 +6033,7 @@
         <v>11</v>
       </c>
       <c r="G2" s="60" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="H2" s="47"/>
       <c r="I2" s="47"/>
@@ -6067,24 +6067,24 @@
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A4" s="4" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="B4" s="5"/>
       <c r="C4" s="5"/>
       <c r="D4" s="6"/>
       <c r="E4" s="5"/>
       <c r="F4" s="62" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="H4" s="5"/>
       <c r="I4" s="5"/>
       <c r="J4" s="6"/>
       <c r="K4" s="5"/>
       <c r="L4" s="62" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.4">
@@ -6092,7 +6092,7 @@
         <v>2</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="D5" s="8"/>
       <c r="E5" s="9" t="s">
@@ -6105,7 +6105,7 @@
         <v>2</v>
       </c>
       <c r="I5" s="8" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="J5" s="8"/>
       <c r="K5" s="9" t="s">
@@ -6173,21 +6173,21 @@
     </row>
     <row r="8" spans="1:12" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A8" s="11" t="s">
-        <v>100</v>
-      </c>
-      <c r="C8" s="137" t="s">
-        <v>105</v>
-      </c>
-      <c r="D8" s="137"/>
-      <c r="E8" s="137"/>
+        <v>97</v>
+      </c>
+      <c r="C8" s="148" t="s">
+        <v>102</v>
+      </c>
+      <c r="D8" s="148"/>
+      <c r="E8" s="148"/>
       <c r="G8" s="11" t="s">
-        <v>100</v>
-      </c>
-      <c r="I8" s="137" t="s">
-        <v>105</v>
-      </c>
-      <c r="J8" s="137"/>
-      <c r="K8" s="137"/>
+        <v>97</v>
+      </c>
+      <c r="I8" s="148" t="s">
+        <v>102</v>
+      </c>
+      <c r="J8" s="148"/>
+      <c r="K8" s="148"/>
     </row>
     <row r="9" spans="1:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A9" s="16" t="s">
@@ -6222,172 +6222,172 @@
       <c r="B10" s="23">
         <v>1</v>
       </c>
-      <c r="C10" s="430" t="s">
+      <c r="C10" s="389" t="s">
         <v>52</v>
       </c>
-      <c r="D10" s="155"/>
-      <c r="E10" s="419"/>
-      <c r="F10" s="420"/>
+      <c r="D10" s="158"/>
+      <c r="E10" s="378"/>
+      <c r="F10" s="379"/>
       <c r="G10" s="22" t="s">
         <v>18</v>
       </c>
       <c r="H10" s="23">
         <v>1</v>
       </c>
-      <c r="I10" s="417"/>
-      <c r="J10" s="418"/>
-      <c r="K10" s="260" t="s">
+      <c r="I10" s="402"/>
+      <c r="J10" s="403"/>
+      <c r="K10" s="344" t="s">
         <v>32</v>
       </c>
-      <c r="L10" s="261"/>
+      <c r="L10" s="345"/>
     </row>
     <row r="11" spans="1:12" ht="15.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="24"/>
       <c r="B11" s="25">
         <v>2</v>
       </c>
-      <c r="C11" s="290" t="s">
+      <c r="C11" s="339" t="s">
         <v>51</v>
       </c>
-      <c r="D11" s="289"/>
-      <c r="E11" s="289" t="s">
-        <v>80</v>
-      </c>
-      <c r="F11" s="382"/>
+      <c r="D11" s="337"/>
+      <c r="E11" s="337" t="s">
+        <v>77</v>
+      </c>
+      <c r="F11" s="375"/>
       <c r="G11" s="24"/>
       <c r="H11" s="25">
         <v>2</v>
       </c>
-      <c r="I11" s="389" t="s">
-        <v>158</v>
-      </c>
-      <c r="J11" s="123"/>
-      <c r="K11" s="289" t="s">
+      <c r="I11" s="361" t="s">
+        <v>154</v>
+      </c>
+      <c r="J11" s="112"/>
+      <c r="K11" s="337" t="s">
         <v>51</v>
       </c>
-      <c r="L11" s="382"/>
+      <c r="L11" s="375"/>
     </row>
     <row r="12" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="24"/>
       <c r="B12" s="25">
         <v>3</v>
       </c>
-      <c r="C12" s="122" t="s">
-        <v>76</v>
-      </c>
-      <c r="D12" s="123"/>
-      <c r="E12" s="311" t="s">
-        <v>80</v>
-      </c>
-      <c r="F12" s="175"/>
+      <c r="C12" s="111" t="s">
+        <v>73</v>
+      </c>
+      <c r="D12" s="112"/>
+      <c r="E12" s="284" t="s">
+        <v>77</v>
+      </c>
+      <c r="F12" s="142"/>
       <c r="G12" s="24"/>
       <c r="H12" s="25">
         <v>3</v>
       </c>
-      <c r="I12" s="389" t="s">
-        <v>158</v>
-      </c>
-      <c r="J12" s="123"/>
-      <c r="K12" s="311" t="s">
+      <c r="I12" s="361" t="s">
+        <v>154</v>
+      </c>
+      <c r="J12" s="112"/>
+      <c r="K12" s="284" t="s">
         <v>53</v>
       </c>
-      <c r="L12" s="175"/>
+      <c r="L12" s="142"/>
     </row>
     <row r="13" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="24"/>
       <c r="B13" s="25">
         <v>4</v>
       </c>
-      <c r="C13" s="244" t="s">
-        <v>158</v>
-      </c>
-      <c r="D13" s="111"/>
-      <c r="E13" s="404" t="s">
+      <c r="C13" s="281" t="s">
+        <v>154</v>
+      </c>
+      <c r="D13" s="113"/>
+      <c r="E13" s="400" t="s">
         <v>53</v>
       </c>
-      <c r="F13" s="416"/>
+      <c r="F13" s="401"/>
       <c r="G13" s="24"/>
       <c r="H13" s="25">
         <v>4</v>
       </c>
-      <c r="I13" s="389" t="s">
-        <v>183</v>
-      </c>
-      <c r="J13" s="311"/>
-      <c r="K13" s="123" t="s">
+      <c r="I13" s="361" t="s">
+        <v>179</v>
+      </c>
+      <c r="J13" s="284"/>
+      <c r="K13" s="112" t="s">
         <v>41</v>
       </c>
-      <c r="L13" s="175"/>
+      <c r="L13" s="142"/>
     </row>
     <row r="14" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="26"/>
       <c r="B14" s="27">
         <v>5</v>
       </c>
-      <c r="C14" s="244" t="s">
-        <v>158</v>
-      </c>
-      <c r="D14" s="245"/>
-      <c r="E14" s="289" t="s">
+      <c r="C14" s="281" t="s">
+        <v>154</v>
+      </c>
+      <c r="D14" s="282"/>
+      <c r="E14" s="337" t="s">
         <v>51</v>
       </c>
-      <c r="F14" s="382"/>
+      <c r="F14" s="375"/>
       <c r="G14" s="26"/>
       <c r="H14" s="27">
         <v>5</v>
       </c>
-      <c r="I14" s="389" t="s">
-        <v>73</v>
-      </c>
-      <c r="J14" s="311"/>
-      <c r="K14" s="289" t="s">
+      <c r="I14" s="361" t="s">
+        <v>70</v>
+      </c>
+      <c r="J14" s="284"/>
+      <c r="K14" s="337" t="s">
         <v>40</v>
       </c>
-      <c r="L14" s="382"/>
+      <c r="L14" s="375"/>
     </row>
     <row r="15" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="26"/>
       <c r="B15" s="27">
         <v>6</v>
       </c>
-      <c r="C15" s="280"/>
-      <c r="D15" s="361"/>
-      <c r="E15" s="362" t="s">
-        <v>74</v>
-      </c>
-      <c r="F15" s="363"/>
+      <c r="C15" s="262"/>
+      <c r="D15" s="390"/>
+      <c r="E15" s="391" t="s">
+        <v>71</v>
+      </c>
+      <c r="F15" s="392"/>
       <c r="G15" s="26"/>
       <c r="H15" s="27">
         <v>6</v>
       </c>
-      <c r="I15" s="247" t="s">
-        <v>73</v>
-      </c>
-      <c r="J15" s="301"/>
-      <c r="K15" s="362" t="s">
-        <v>204</v>
-      </c>
-      <c r="L15" s="363"/>
+      <c r="I15" s="321" t="s">
+        <v>70</v>
+      </c>
+      <c r="J15" s="322"/>
+      <c r="K15" s="391" t="s">
+        <v>199</v>
+      </c>
+      <c r="L15" s="392"/>
     </row>
     <row r="16" spans="1:12" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A16" s="28"/>
       <c r="B16" s="29"/>
-      <c r="C16" s="414"/>
-      <c r="D16" s="415"/>
-      <c r="E16" s="423" t="s">
+      <c r="C16" s="398"/>
+      <c r="D16" s="399"/>
+      <c r="E16" s="359" t="s">
         <v>32</v>
       </c>
-      <c r="F16" s="424"/>
+      <c r="F16" s="360"/>
       <c r="G16" s="28"/>
       <c r="H16" s="29">
         <v>7</v>
       </c>
-      <c r="I16" s="432"/>
-      <c r="J16" s="433"/>
-      <c r="K16" s="423" t="s">
-        <v>79</v>
-      </c>
-      <c r="L16" s="424"/>
+      <c r="I16" s="362"/>
+      <c r="J16" s="363"/>
+      <c r="K16" s="359" t="s">
+        <v>76</v>
+      </c>
+      <c r="L16" s="360"/>
     </row>
     <row r="17" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="30" t="s">
@@ -6396,90 +6396,90 @@
       <c r="B17" s="58" t="s">
         <v>64</v>
       </c>
-      <c r="C17" s="184" t="s">
+      <c r="C17" s="162" t="s">
         <v>65</v>
       </c>
-      <c r="D17" s="185"/>
-      <c r="E17" s="185"/>
-      <c r="F17" s="186"/>
+      <c r="D17" s="163"/>
+      <c r="E17" s="163"/>
+      <c r="F17" s="164"/>
       <c r="G17" s="30" t="s">
         <v>19</v>
       </c>
       <c r="H17" s="58" t="s">
         <v>64</v>
       </c>
-      <c r="I17" s="184" t="s">
+      <c r="I17" s="162" t="s">
         <v>65</v>
       </c>
-      <c r="J17" s="185"/>
-      <c r="K17" s="185"/>
-      <c r="L17" s="186"/>
+      <c r="J17" s="163"/>
+      <c r="K17" s="163"/>
+      <c r="L17" s="164"/>
     </row>
     <row r="18" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="24"/>
       <c r="B18" s="25">
         <v>4</v>
       </c>
-      <c r="C18" s="264" t="s">
-        <v>165</v>
-      </c>
-      <c r="D18" s="265"/>
-      <c r="E18" s="265"/>
-      <c r="F18" s="268"/>
+      <c r="C18" s="296" t="s">
+        <v>161</v>
+      </c>
+      <c r="D18" s="297"/>
+      <c r="E18" s="297"/>
+      <c r="F18" s="338"/>
       <c r="G18" s="24"/>
       <c r="H18" s="25">
         <v>4</v>
       </c>
-      <c r="I18" s="264" t="s">
-        <v>165</v>
-      </c>
-      <c r="J18" s="265"/>
-      <c r="K18" s="265"/>
-      <c r="L18" s="268"/>
+      <c r="I18" s="296" t="s">
+        <v>161</v>
+      </c>
+      <c r="J18" s="297"/>
+      <c r="K18" s="297"/>
+      <c r="L18" s="338"/>
     </row>
     <row r="19" spans="1:12" ht="30.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="24"/>
       <c r="B19" s="25">
         <v>5</v>
       </c>
-      <c r="C19" s="264" t="s">
-        <v>166</v>
-      </c>
-      <c r="D19" s="265"/>
-      <c r="E19" s="265"/>
-      <c r="F19" s="268"/>
+      <c r="C19" s="296" t="s">
+        <v>162</v>
+      </c>
+      <c r="D19" s="297"/>
+      <c r="E19" s="297"/>
+      <c r="F19" s="338"/>
       <c r="G19" s="24"/>
       <c r="H19" s="25">
         <v>5</v>
       </c>
-      <c r="I19" s="264" t="s">
-        <v>166</v>
-      </c>
-      <c r="J19" s="265"/>
-      <c r="K19" s="265"/>
-      <c r="L19" s="268"/>
+      <c r="I19" s="296" t="s">
+        <v>162</v>
+      </c>
+      <c r="J19" s="297"/>
+      <c r="K19" s="297"/>
+      <c r="L19" s="338"/>
     </row>
     <row r="20" spans="1:12" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A20" s="24"/>
       <c r="B20" s="25">
         <v>6</v>
       </c>
-      <c r="C20" s="280" t="s">
-        <v>167</v>
-      </c>
-      <c r="D20" s="428"/>
-      <c r="E20" s="428"/>
-      <c r="F20" s="429"/>
+      <c r="C20" s="262" t="s">
+        <v>163</v>
+      </c>
+      <c r="D20" s="387"/>
+      <c r="E20" s="387"/>
+      <c r="F20" s="388"/>
       <c r="G20" s="24"/>
       <c r="H20" s="25">
         <v>6</v>
       </c>
-      <c r="I20" s="425" t="s">
-        <v>167</v>
-      </c>
-      <c r="J20" s="426"/>
-      <c r="K20" s="426"/>
-      <c r="L20" s="427"/>
+      <c r="I20" s="384" t="s">
+        <v>163</v>
+      </c>
+      <c r="J20" s="385"/>
+      <c r="K20" s="385"/>
+      <c r="L20" s="386"/>
     </row>
     <row r="21" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="30" t="s">
@@ -6488,72 +6488,72 @@
       <c r="B21" s="31">
         <v>1</v>
       </c>
-      <c r="C21" s="317"/>
-      <c r="D21" s="120"/>
-      <c r="E21" s="260" t="s">
-        <v>74</v>
-      </c>
-      <c r="F21" s="422"/>
+      <c r="C21" s="290"/>
+      <c r="D21" s="214"/>
+      <c r="E21" s="344" t="s">
+        <v>71</v>
+      </c>
+      <c r="F21" s="381"/>
       <c r="G21" s="30" t="s">
         <v>20</v>
       </c>
       <c r="H21" s="31">
         <v>1</v>
       </c>
-      <c r="I21" s="287" t="s">
+      <c r="I21" s="335" t="s">
         <v>32</v>
       </c>
-      <c r="J21" s="288"/>
-      <c r="K21" s="394"/>
-      <c r="L21" s="395"/>
+      <c r="J21" s="336"/>
+      <c r="K21" s="382"/>
+      <c r="L21" s="383"/>
     </row>
     <row r="22" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="24"/>
       <c r="B22" s="25">
         <v>2</v>
       </c>
-      <c r="C22" s="244" t="s">
+      <c r="C22" s="281" t="s">
         <v>41</v>
       </c>
-      <c r="D22" s="111"/>
-      <c r="E22" s="245"/>
-      <c r="F22" s="112"/>
+      <c r="D22" s="113"/>
+      <c r="E22" s="282"/>
+      <c r="F22" s="114"/>
       <c r="G22" s="24"/>
       <c r="H22" s="25">
         <v>2</v>
       </c>
-      <c r="I22" s="389" t="s">
-        <v>74</v>
-      </c>
-      <c r="J22" s="123"/>
-      <c r="K22" s="265" t="s">
-        <v>163</v>
-      </c>
-      <c r="L22" s="268"/>
+      <c r="I22" s="361" t="s">
+        <v>71</v>
+      </c>
+      <c r="J22" s="112"/>
+      <c r="K22" s="297" t="s">
+        <v>159</v>
+      </c>
+      <c r="L22" s="338"/>
     </row>
     <row r="23" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="24"/>
       <c r="B23" s="25">
         <v>3</v>
       </c>
-      <c r="C23" s="244" t="s">
+      <c r="C23" s="281" t="s">
         <v>42</v>
       </c>
-      <c r="D23" s="111"/>
-      <c r="E23" s="245" t="s">
-        <v>75</v>
-      </c>
-      <c r="F23" s="112"/>
+      <c r="D23" s="113"/>
+      <c r="E23" s="282" t="s">
+        <v>72</v>
+      </c>
+      <c r="F23" s="114"/>
       <c r="G23" s="24"/>
       <c r="H23" s="25">
         <v>3</v>
       </c>
-      <c r="I23" s="389" t="s">
-        <v>74</v>
-      </c>
-      <c r="J23" s="123"/>
+      <c r="I23" s="361" t="s">
+        <v>71</v>
+      </c>
+      <c r="J23" s="112"/>
       <c r="K23" s="396" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="L23" s="397"/>
     </row>
@@ -6562,74 +6562,74 @@
       <c r="B24" s="25">
         <v>4</v>
       </c>
-      <c r="C24" s="389" t="s">
-        <v>159</v>
-      </c>
-      <c r="D24" s="123"/>
-      <c r="E24" s="245" t="s">
-        <v>75</v>
-      </c>
-      <c r="F24" s="112"/>
+      <c r="C24" s="361" t="s">
+        <v>155</v>
+      </c>
+      <c r="D24" s="112"/>
+      <c r="E24" s="282" t="s">
+        <v>72</v>
+      </c>
+      <c r="F24" s="114"/>
       <c r="G24" s="24"/>
       <c r="H24" s="25">
         <v>4</v>
       </c>
-      <c r="I24" s="389" t="s">
-        <v>170</v>
-      </c>
-      <c r="J24" s="311"/>
-      <c r="K24" s="251"/>
-      <c r="L24" s="421"/>
+      <c r="I24" s="361" t="s">
+        <v>166</v>
+      </c>
+      <c r="J24" s="284"/>
+      <c r="K24" s="356"/>
+      <c r="L24" s="380"/>
     </row>
     <row r="25" spans="1:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="24"/>
       <c r="B25" s="25">
         <v>5</v>
       </c>
-      <c r="C25" s="389" t="s">
-        <v>203</v>
-      </c>
-      <c r="D25" s="123"/>
-      <c r="E25" s="289" t="s">
-        <v>78</v>
-      </c>
-      <c r="F25" s="382"/>
+      <c r="C25" s="361" t="s">
+        <v>198</v>
+      </c>
+      <c r="D25" s="112"/>
+      <c r="E25" s="337" t="s">
+        <v>75</v>
+      </c>
+      <c r="F25" s="375"/>
       <c r="G25" s="24"/>
       <c r="H25" s="25">
         <v>5</v>
       </c>
-      <c r="I25" s="239" t="s">
-        <v>170</v>
-      </c>
-      <c r="J25" s="241"/>
-      <c r="K25" s="241" t="s">
-        <v>75</v>
-      </c>
-      <c r="L25" s="398"/>
+      <c r="I25" s="353" t="s">
+        <v>166</v>
+      </c>
+      <c r="J25" s="354"/>
+      <c r="K25" s="354" t="s">
+        <v>72</v>
+      </c>
+      <c r="L25" s="404"/>
     </row>
     <row r="26" spans="1:12" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A26" s="24"/>
       <c r="B26" s="25">
         <v>6</v>
       </c>
-      <c r="C26" s="440" t="s">
-        <v>79</v>
-      </c>
-      <c r="D26" s="441"/>
-      <c r="E26" s="442"/>
-      <c r="F26" s="443"/>
+      <c r="C26" s="371" t="s">
+        <v>76</v>
+      </c>
+      <c r="D26" s="372"/>
+      <c r="E26" s="373"/>
+      <c r="F26" s="374"/>
       <c r="G26" s="26"/>
       <c r="H26" s="27">
         <v>6</v>
       </c>
-      <c r="I26" s="399" t="s">
-        <v>184</v>
-      </c>
-      <c r="J26" s="400"/>
-      <c r="K26" s="401" t="s">
-        <v>75</v>
-      </c>
-      <c r="L26" s="402"/>
+      <c r="I26" s="405" t="s">
+        <v>180</v>
+      </c>
+      <c r="J26" s="406"/>
+      <c r="K26" s="407" t="s">
+        <v>72</v>
+      </c>
+      <c r="L26" s="408"/>
     </row>
     <row r="27" spans="1:12" ht="14.45" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A27" s="30" t="s">
@@ -6638,92 +6638,92 @@
       <c r="B27" s="31">
         <v>1</v>
       </c>
-      <c r="C27" s="287"/>
-      <c r="D27" s="285"/>
-      <c r="E27" s="285"/>
-      <c r="F27" s="393"/>
+      <c r="C27" s="335"/>
+      <c r="D27" s="333"/>
+      <c r="E27" s="333"/>
+      <c r="F27" s="416"/>
       <c r="G27" s="30" t="s">
         <v>21</v>
       </c>
       <c r="H27" s="31">
         <v>1</v>
       </c>
-      <c r="I27" s="438"/>
-      <c r="J27" s="439"/>
-      <c r="K27" s="392" t="s">
-        <v>171</v>
-      </c>
-      <c r="L27" s="205"/>
+      <c r="I27" s="369"/>
+      <c r="J27" s="370"/>
+      <c r="K27" s="415" t="s">
+        <v>167</v>
+      </c>
+      <c r="L27" s="122"/>
     </row>
     <row r="28" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A28" s="24"/>
       <c r="B28" s="23">
         <v>2</v>
       </c>
-      <c r="C28" s="444" t="s">
-        <v>170</v>
-      </c>
-      <c r="D28" s="445"/>
+      <c r="C28" s="376" t="s">
+        <v>166</v>
+      </c>
+      <c r="D28" s="377"/>
       <c r="E28" s="396" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="F28" s="397"/>
       <c r="G28" s="24"/>
       <c r="H28" s="23">
         <v>2</v>
       </c>
-      <c r="I28" s="437"/>
-      <c r="J28" s="266"/>
-      <c r="K28" s="390" t="s">
-        <v>171</v>
-      </c>
-      <c r="L28" s="391"/>
+      <c r="I28" s="368"/>
+      <c r="J28" s="348"/>
+      <c r="K28" s="413" t="s">
+        <v>167</v>
+      </c>
+      <c r="L28" s="414"/>
     </row>
     <row r="29" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A29" s="24"/>
       <c r="B29" s="25">
         <v>3</v>
       </c>
-      <c r="C29" s="389" t="s">
-        <v>170</v>
-      </c>
-      <c r="D29" s="311"/>
-      <c r="E29" s="241" t="s">
-        <v>160</v>
-      </c>
-      <c r="F29" s="398"/>
+      <c r="C29" s="361" t="s">
+        <v>166</v>
+      </c>
+      <c r="D29" s="284"/>
+      <c r="E29" s="354" t="s">
+        <v>156</v>
+      </c>
+      <c r="F29" s="404"/>
       <c r="G29" s="24"/>
       <c r="H29" s="25">
         <v>3</v>
       </c>
-      <c r="I29" s="389"/>
-      <c r="J29" s="123"/>
-      <c r="K29" s="265" t="s">
-        <v>78</v>
-      </c>
-      <c r="L29" s="268"/>
+      <c r="I29" s="361"/>
+      <c r="J29" s="112"/>
+      <c r="K29" s="297" t="s">
+        <v>75</v>
+      </c>
+      <c r="L29" s="338"/>
     </row>
     <row r="30" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A30" s="24"/>
       <c r="B30" s="25">
         <v>4</v>
       </c>
-      <c r="C30" s="403" t="s">
-        <v>77</v>
+      <c r="C30" s="409" t="s">
+        <v>74</v>
       </c>
       <c r="D30" s="396"/>
-      <c r="E30" s="404" t="s">
-        <v>161</v>
-      </c>
-      <c r="F30" s="405"/>
+      <c r="E30" s="400" t="s">
+        <v>157</v>
+      </c>
+      <c r="F30" s="410"/>
       <c r="G30" s="24"/>
       <c r="H30" s="25">
         <v>4</v>
       </c>
-      <c r="I30" s="389" t="s">
-        <v>159</v>
-      </c>
-      <c r="J30" s="123"/>
+      <c r="I30" s="361" t="s">
+        <v>155</v>
+      </c>
+      <c r="J30" s="112"/>
       <c r="K30" s="396"/>
       <c r="L30" s="397"/>
     </row>
@@ -6732,66 +6732,66 @@
       <c r="B31" s="25">
         <v>5</v>
       </c>
-      <c r="C31" s="244" t="s">
-        <v>79</v>
-      </c>
-      <c r="D31" s="111"/>
-      <c r="E31" s="241" t="s">
-        <v>79</v>
-      </c>
-      <c r="F31" s="398"/>
+      <c r="C31" s="281" t="s">
+        <v>76</v>
+      </c>
+      <c r="D31" s="113"/>
+      <c r="E31" s="354" t="s">
+        <v>76</v>
+      </c>
+      <c r="F31" s="404"/>
       <c r="G31" s="24"/>
       <c r="H31" s="25">
         <v>5</v>
       </c>
-      <c r="I31" s="389" t="s">
-        <v>159</v>
-      </c>
-      <c r="J31" s="123"/>
-      <c r="K31" s="408"/>
-      <c r="L31" s="409"/>
+      <c r="I31" s="361" t="s">
+        <v>155</v>
+      </c>
+      <c r="J31" s="112"/>
+      <c r="K31" s="411"/>
+      <c r="L31" s="412"/>
     </row>
     <row r="32" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A32" s="26"/>
       <c r="B32" s="27">
         <v>6</v>
       </c>
-      <c r="C32" s="280" t="s">
-        <v>162</v>
-      </c>
-      <c r="D32" s="361"/>
-      <c r="E32" s="364"/>
-      <c r="F32" s="365"/>
+      <c r="C32" s="262" t="s">
+        <v>158</v>
+      </c>
+      <c r="D32" s="390"/>
+      <c r="E32" s="431"/>
+      <c r="F32" s="432"/>
       <c r="G32" s="26"/>
       <c r="H32" s="27">
         <v>6</v>
       </c>
-      <c r="I32" s="366" t="s">
-        <v>157</v>
-      </c>
-      <c r="J32" s="367"/>
-      <c r="K32" s="368"/>
-      <c r="L32" s="369"/>
+      <c r="I32" s="433" t="s">
+        <v>153</v>
+      </c>
+      <c r="J32" s="434"/>
+      <c r="K32" s="435"/>
+      <c r="L32" s="436"/>
     </row>
     <row r="33" spans="1:12" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A33" s="32"/>
       <c r="B33" s="29"/>
-      <c r="C33" s="376" t="s">
+      <c r="C33" s="443" t="s">
         <v>32</v>
       </c>
-      <c r="D33" s="194"/>
-      <c r="E33" s="294"/>
-      <c r="F33" s="406"/>
+      <c r="D33" s="131"/>
+      <c r="E33" s="314"/>
+      <c r="F33" s="444"/>
       <c r="G33" s="32"/>
       <c r="H33" s="29">
         <v>7</v>
       </c>
-      <c r="I33" s="407" t="s">
+      <c r="I33" s="445" t="s">
         <v>41</v>
       </c>
-      <c r="J33" s="283"/>
-      <c r="K33" s="370"/>
-      <c r="L33" s="371"/>
+      <c r="J33" s="331"/>
+      <c r="K33" s="437"/>
+      <c r="L33" s="438"/>
     </row>
     <row r="34" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A34" s="30" t="s">
@@ -6800,134 +6800,134 @@
       <c r="B34" s="31">
         <v>1</v>
       </c>
-      <c r="C34" s="372"/>
-      <c r="D34" s="373"/>
-      <c r="E34" s="374" t="s">
+      <c r="C34" s="439"/>
+      <c r="D34" s="440"/>
+      <c r="E34" s="441" t="s">
         <v>40</v>
       </c>
-      <c r="F34" s="375"/>
+      <c r="F34" s="442"/>
       <c r="G34" s="30" t="s">
         <v>22</v>
       </c>
       <c r="H34" s="31">
         <v>1</v>
       </c>
-      <c r="I34" s="317"/>
-      <c r="J34" s="120"/>
-      <c r="K34" s="394"/>
-      <c r="L34" s="395"/>
+      <c r="I34" s="290"/>
+      <c r="J34" s="214"/>
+      <c r="K34" s="382"/>
+      <c r="L34" s="383"/>
     </row>
     <row r="35" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A35" s="33"/>
       <c r="B35" s="25">
         <v>2</v>
       </c>
-      <c r="C35" s="254" t="s">
-        <v>85</v>
-      </c>
-      <c r="D35" s="255"/>
-      <c r="E35" s="289" t="s">
-        <v>175</v>
-      </c>
-      <c r="F35" s="382"/>
+      <c r="C35" s="264" t="s">
+        <v>82</v>
+      </c>
+      <c r="D35" s="328"/>
+      <c r="E35" s="337" t="s">
+        <v>171</v>
+      </c>
+      <c r="F35" s="375"/>
       <c r="G35" s="33"/>
       <c r="H35" s="25">
         <v>2</v>
       </c>
-      <c r="I35" s="244" t="s">
+      <c r="I35" s="281" t="s">
         <v>32</v>
       </c>
-      <c r="J35" s="111"/>
-      <c r="K35" s="245" t="s">
+      <c r="J35" s="113"/>
+      <c r="K35" s="282" t="s">
         <v>54</v>
       </c>
-      <c r="L35" s="246"/>
+      <c r="L35" s="320"/>
     </row>
     <row r="36" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A36" s="33"/>
       <c r="B36" s="25">
         <v>3</v>
       </c>
-      <c r="C36" s="262"/>
-      <c r="D36" s="263"/>
-      <c r="E36" s="383" t="s">
-        <v>84</v>
-      </c>
-      <c r="F36" s="273"/>
+      <c r="C36" s="346"/>
+      <c r="D36" s="347"/>
+      <c r="E36" s="430" t="s">
+        <v>81</v>
+      </c>
+      <c r="F36" s="266"/>
       <c r="G36" s="33"/>
       <c r="H36" s="25">
         <v>3</v>
       </c>
-      <c r="I36" s="244" t="s">
-        <v>172</v>
-      </c>
-      <c r="J36" s="245"/>
-      <c r="K36" s="245"/>
-      <c r="L36" s="246"/>
+      <c r="I36" s="281" t="s">
+        <v>168</v>
+      </c>
+      <c r="J36" s="282"/>
+      <c r="K36" s="282"/>
+      <c r="L36" s="320"/>
     </row>
     <row r="37" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A37" s="34"/>
       <c r="B37" s="27">
         <v>4</v>
       </c>
-      <c r="C37" s="264" t="s">
-        <v>156</v>
-      </c>
-      <c r="D37" s="265"/>
-      <c r="E37" s="265"/>
-      <c r="F37" s="268"/>
+      <c r="C37" s="296" t="s">
+        <v>152</v>
+      </c>
+      <c r="D37" s="297"/>
+      <c r="E37" s="297"/>
+      <c r="F37" s="338"/>
       <c r="G37" s="34"/>
       <c r="H37" s="27">
         <v>4</v>
       </c>
-      <c r="I37" s="264" t="s">
-        <v>156</v>
-      </c>
-      <c r="J37" s="265"/>
-      <c r="K37" s="265"/>
-      <c r="L37" s="268"/>
+      <c r="I37" s="296" t="s">
+        <v>152</v>
+      </c>
+      <c r="J37" s="297"/>
+      <c r="K37" s="297"/>
+      <c r="L37" s="338"/>
     </row>
     <row r="38" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A38" s="34"/>
       <c r="B38" s="27">
         <v>5</v>
       </c>
-      <c r="C38" s="254" t="s">
-        <v>168</v>
-      </c>
-      <c r="D38" s="272"/>
-      <c r="E38" s="272"/>
-      <c r="F38" s="273"/>
+      <c r="C38" s="264" t="s">
+        <v>164</v>
+      </c>
+      <c r="D38" s="265"/>
+      <c r="E38" s="265"/>
+      <c r="F38" s="266"/>
       <c r="G38" s="34"/>
       <c r="H38" s="27">
         <v>5</v>
       </c>
-      <c r="I38" s="264" t="s">
-        <v>202</v>
-      </c>
-      <c r="J38" s="265"/>
-      <c r="K38" s="265"/>
-      <c r="L38" s="268"/>
+      <c r="I38" s="296" t="s">
+        <v>197</v>
+      </c>
+      <c r="J38" s="297"/>
+      <c r="K38" s="297"/>
+      <c r="L38" s="338"/>
     </row>
     <row r="39" spans="1:12" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A39" s="35"/>
       <c r="B39" s="29">
         <v>6</v>
       </c>
-      <c r="C39" s="386"/>
-      <c r="D39" s="387"/>
-      <c r="E39" s="387"/>
-      <c r="F39" s="388"/>
+      <c r="C39" s="425"/>
+      <c r="D39" s="426"/>
+      <c r="E39" s="426"/>
+      <c r="F39" s="427"/>
       <c r="G39" s="35"/>
       <c r="H39" s="29">
         <v>6</v>
       </c>
-      <c r="I39" s="358" t="s">
-        <v>201</v>
-      </c>
-      <c r="J39" s="359"/>
-      <c r="K39" s="359"/>
-      <c r="L39" s="360"/>
+      <c r="I39" s="417" t="s">
+        <v>196</v>
+      </c>
+      <c r="J39" s="428"/>
+      <c r="K39" s="428"/>
+      <c r="L39" s="429"/>
     </row>
     <row r="40" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A40" s="42" t="s">
@@ -6936,174 +6936,174 @@
       <c r="B40" s="31">
         <v>1</v>
       </c>
-      <c r="C40" s="380" t="s">
-        <v>86</v>
-      </c>
-      <c r="D40" s="381"/>
-      <c r="E40" s="384"/>
-      <c r="F40" s="385"/>
+      <c r="C40" s="421" t="s">
+        <v>83</v>
+      </c>
+      <c r="D40" s="422"/>
+      <c r="E40" s="423"/>
+      <c r="F40" s="424"/>
       <c r="G40" s="42" t="s">
         <v>23</v>
       </c>
       <c r="H40" s="31">
         <v>2</v>
       </c>
-      <c r="I40" s="434" t="s">
-        <v>169</v>
-      </c>
-      <c r="J40" s="435"/>
-      <c r="K40" s="435"/>
-      <c r="L40" s="436"/>
+      <c r="I40" s="364" t="s">
+        <v>165</v>
+      </c>
+      <c r="J40" s="365"/>
+      <c r="K40" s="365"/>
+      <c r="L40" s="366"/>
     </row>
     <row r="41" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A41" s="37"/>
       <c r="B41" s="25">
         <v>2</v>
       </c>
-      <c r="C41" s="244" t="s">
-        <v>86</v>
-      </c>
-      <c r="D41" s="245"/>
-      <c r="E41" s="245" t="s">
-        <v>173</v>
-      </c>
-      <c r="F41" s="246"/>
+      <c r="C41" s="281" t="s">
+        <v>83</v>
+      </c>
+      <c r="D41" s="282"/>
+      <c r="E41" s="282" t="s">
+        <v>169</v>
+      </c>
+      <c r="F41" s="320"/>
       <c r="G41" s="37"/>
       <c r="H41" s="25">
         <v>3</v>
       </c>
-      <c r="I41" s="410" t="s">
-        <v>169</v>
-      </c>
-      <c r="J41" s="89"/>
-      <c r="K41" s="89"/>
-      <c r="L41" s="90"/>
+      <c r="I41" s="367" t="s">
+        <v>165</v>
+      </c>
+      <c r="J41" s="106"/>
+      <c r="K41" s="106"/>
+      <c r="L41" s="107"/>
     </row>
     <row r="42" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A42" s="37"/>
       <c r="B42" s="25">
         <v>3</v>
       </c>
-      <c r="C42" s="290" t="s">
-        <v>81</v>
-      </c>
-      <c r="D42" s="289"/>
-      <c r="E42" s="289"/>
-      <c r="F42" s="382"/>
+      <c r="C42" s="339" t="s">
+        <v>78</v>
+      </c>
+      <c r="D42" s="337"/>
+      <c r="E42" s="337"/>
+      <c r="F42" s="375"/>
       <c r="G42" s="37"/>
       <c r="H42" s="25">
         <v>4</v>
       </c>
-      <c r="I42" s="389" t="s">
-        <v>174</v>
-      </c>
-      <c r="J42" s="123"/>
-      <c r="K42" s="249" t="s">
-        <v>83</v>
-      </c>
-      <c r="L42" s="90"/>
+      <c r="I42" s="361" t="s">
+        <v>170</v>
+      </c>
+      <c r="J42" s="112"/>
+      <c r="K42" s="278" t="s">
+        <v>80</v>
+      </c>
+      <c r="L42" s="107"/>
     </row>
     <row r="43" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A43" s="37"/>
       <c r="B43" s="25">
         <v>4</v>
       </c>
-      <c r="C43" s="410" t="s">
-        <v>169</v>
-      </c>
-      <c r="D43" s="89"/>
-      <c r="E43" s="89"/>
-      <c r="F43" s="90"/>
+      <c r="C43" s="367" t="s">
+        <v>165</v>
+      </c>
+      <c r="D43" s="106"/>
+      <c r="E43" s="106"/>
+      <c r="F43" s="107"/>
       <c r="G43" s="37"/>
       <c r="H43" s="25">
         <v>5</v>
       </c>
-      <c r="I43" s="290" t="s">
+      <c r="I43" s="339" t="s">
         <v>51</v>
       </c>
-      <c r="J43" s="289"/>
-      <c r="K43" s="311" t="s">
-        <v>200</v>
-      </c>
-      <c r="L43" s="175"/>
+      <c r="J43" s="337"/>
+      <c r="K43" s="284" t="s">
+        <v>195</v>
+      </c>
+      <c r="L43" s="142"/>
     </row>
     <row r="44" spans="1:12" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A44" s="63"/>
       <c r="B44" s="29">
         <v>5</v>
       </c>
-      <c r="C44" s="358" t="s">
-        <v>169</v>
-      </c>
-      <c r="D44" s="95"/>
-      <c r="E44" s="95"/>
-      <c r="F44" s="96"/>
+      <c r="C44" s="417" t="s">
+        <v>165</v>
+      </c>
+      <c r="D44" s="100"/>
+      <c r="E44" s="100"/>
+      <c r="F44" s="101"/>
       <c r="G44" s="63"/>
       <c r="H44" s="29">
         <v>6</v>
       </c>
-      <c r="I44" s="269" t="s">
-        <v>82</v>
-      </c>
-      <c r="J44" s="270"/>
-      <c r="K44" s="270" t="s">
-        <v>162</v>
-      </c>
-      <c r="L44" s="207"/>
+      <c r="I44" s="350" t="s">
+        <v>79</v>
+      </c>
+      <c r="J44" s="351"/>
+      <c r="K44" s="351" t="s">
+        <v>158</v>
+      </c>
+      <c r="L44" s="126"/>
     </row>
     <row r="45" spans="1:12" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A45" s="66"/>
       <c r="B45" s="67"/>
-      <c r="C45" s="411"/>
-      <c r="D45" s="412"/>
-      <c r="E45" s="412"/>
-      <c r="F45" s="413"/>
+      <c r="C45" s="393"/>
+      <c r="D45" s="394"/>
+      <c r="E45" s="394"/>
+      <c r="F45" s="395"/>
       <c r="G45" s="66"/>
       <c r="H45" s="67"/>
-      <c r="I45" s="377"/>
-      <c r="J45" s="378"/>
-      <c r="K45" s="378"/>
-      <c r="L45" s="379"/>
+      <c r="I45" s="418"/>
+      <c r="J45" s="419"/>
+      <c r="K45" s="419"/>
+      <c r="L45" s="420"/>
     </row>
     <row r="46" spans="1:12" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A46" s="52"/>
       <c r="B46" s="29" t="s">
         <v>27</v>
       </c>
-      <c r="C46" s="229" t="s">
+      <c r="C46" s="78" t="s">
         <v>50</v>
       </c>
-      <c r="D46" s="230"/>
-      <c r="E46" s="230"/>
-      <c r="F46" s="231"/>
+      <c r="D46" s="79"/>
+      <c r="E46" s="79"/>
+      <c r="F46" s="80"/>
       <c r="G46" s="52"/>
       <c r="H46" s="29" t="s">
         <v>27</v>
       </c>
-      <c r="I46" s="229" t="s">
+      <c r="I46" s="78" t="s">
         <v>50</v>
       </c>
-      <c r="J46" s="230"/>
-      <c r="K46" s="230"/>
-      <c r="L46" s="231"/>
+      <c r="J46" s="79"/>
+      <c r="K46" s="79"/>
+      <c r="L46" s="80"/>
     </row>
     <row r="47" spans="1:12" ht="41.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A47" s="431" t="s">
-        <v>205</v>
-      </c>
-      <c r="B47" s="431"/>
-      <c r="C47" s="431"/>
-      <c r="D47" s="431"/>
-      <c r="E47" s="431"/>
-      <c r="F47" s="431"/>
-      <c r="G47" s="431" t="s">
-        <v>205</v>
-      </c>
-      <c r="H47" s="431"/>
-      <c r="I47" s="431"/>
-      <c r="J47" s="431"/>
-      <c r="K47" s="431"/>
-      <c r="L47" s="431"/>
+      <c r="A47" s="358" t="s">
+        <v>200</v>
+      </c>
+      <c r="B47" s="358"/>
+      <c r="C47" s="358"/>
+      <c r="D47" s="358"/>
+      <c r="E47" s="358"/>
+      <c r="F47" s="358"/>
+      <c r="G47" s="358" t="s">
+        <v>200</v>
+      </c>
+      <c r="H47" s="358"/>
+      <c r="I47" s="358"/>
+      <c r="J47" s="358"/>
+      <c r="K47" s="358"/>
+      <c r="L47" s="358"/>
     </row>
     <row r="48" spans="1:12" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A48" s="2" t="s">
@@ -7135,6 +7135,110 @@
     </row>
   </sheetData>
   <mergeCells count="128">
+    <mergeCell ref="I36:L36"/>
+    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="E35:F35"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="E36:F36"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="I15:J15"/>
+    <mergeCell ref="K15:L15"/>
+    <mergeCell ref="C32:D32"/>
+    <mergeCell ref="E32:F32"/>
+    <mergeCell ref="I32:J32"/>
+    <mergeCell ref="K32:L32"/>
+    <mergeCell ref="K33:L33"/>
+    <mergeCell ref="C34:D34"/>
+    <mergeCell ref="E34:F34"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="I34:J34"/>
+    <mergeCell ref="K34:L34"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="E29:F29"/>
+    <mergeCell ref="E33:F33"/>
+    <mergeCell ref="I33:J33"/>
+    <mergeCell ref="I35:J35"/>
+    <mergeCell ref="C44:F44"/>
+    <mergeCell ref="I45:L45"/>
+    <mergeCell ref="I44:J44"/>
+    <mergeCell ref="K44:L44"/>
+    <mergeCell ref="C41:D41"/>
+    <mergeCell ref="E41:F41"/>
+    <mergeCell ref="C40:D40"/>
+    <mergeCell ref="C37:F37"/>
+    <mergeCell ref="I37:L37"/>
+    <mergeCell ref="E40:F40"/>
+    <mergeCell ref="C39:F39"/>
+    <mergeCell ref="C38:F38"/>
+    <mergeCell ref="I38:L38"/>
+    <mergeCell ref="I39:J39"/>
+    <mergeCell ref="K39:L39"/>
+    <mergeCell ref="K35:L35"/>
+    <mergeCell ref="K25:L25"/>
+    <mergeCell ref="I26:J26"/>
+    <mergeCell ref="K26:L26"/>
+    <mergeCell ref="I30:J30"/>
+    <mergeCell ref="K30:L30"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="I31:J31"/>
+    <mergeCell ref="E30:F30"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="K31:L31"/>
+    <mergeCell ref="K28:L28"/>
+    <mergeCell ref="K27:L27"/>
+    <mergeCell ref="I29:J29"/>
+    <mergeCell ref="K29:L29"/>
+    <mergeCell ref="C27:F27"/>
+    <mergeCell ref="C46:F46"/>
+    <mergeCell ref="C43:F43"/>
+    <mergeCell ref="C45:F45"/>
+    <mergeCell ref="I43:J43"/>
+    <mergeCell ref="K43:L43"/>
+    <mergeCell ref="I42:J42"/>
+    <mergeCell ref="K42:L42"/>
+    <mergeCell ref="C8:E8"/>
+    <mergeCell ref="I8:K8"/>
+    <mergeCell ref="I21:J21"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="I22:J22"/>
+    <mergeCell ref="K22:L22"/>
+    <mergeCell ref="I23:J23"/>
+    <mergeCell ref="K23:L23"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="E13:F13"/>
+    <mergeCell ref="K10:L10"/>
+    <mergeCell ref="K11:L11"/>
+    <mergeCell ref="K12:L12"/>
+    <mergeCell ref="I10:J10"/>
+    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="I12:J12"/>
+    <mergeCell ref="E10:F10"/>
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="E12:F12"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="K24:L24"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="I24:J24"/>
+    <mergeCell ref="K21:L21"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="I20:L20"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="C20:F20"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="E14:F14"/>
+    <mergeCell ref="I14:J14"/>
+    <mergeCell ref="K14:L14"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="E15:F15"/>
     <mergeCell ref="A47:F47"/>
     <mergeCell ref="G47:L47"/>
     <mergeCell ref="K13:L13"/>
@@ -7159,110 +7263,6 @@
     <mergeCell ref="C28:D28"/>
     <mergeCell ref="I46:L46"/>
     <mergeCell ref="C42:F42"/>
-    <mergeCell ref="E10:F10"/>
-    <mergeCell ref="E11:F11"/>
-    <mergeCell ref="E12:F12"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="K24:L24"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="I24:J24"/>
-    <mergeCell ref="K21:L21"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="I20:L20"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="C20:F20"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="E14:F14"/>
-    <mergeCell ref="I14:J14"/>
-    <mergeCell ref="K14:L14"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="C46:F46"/>
-    <mergeCell ref="C43:F43"/>
-    <mergeCell ref="C45:F45"/>
-    <mergeCell ref="I43:J43"/>
-    <mergeCell ref="K43:L43"/>
-    <mergeCell ref="I42:J42"/>
-    <mergeCell ref="K42:L42"/>
-    <mergeCell ref="C8:E8"/>
-    <mergeCell ref="I8:K8"/>
-    <mergeCell ref="I21:J21"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="I22:J22"/>
-    <mergeCell ref="K22:L22"/>
-    <mergeCell ref="I23:J23"/>
-    <mergeCell ref="K23:L23"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E13:F13"/>
-    <mergeCell ref="K10:L10"/>
-    <mergeCell ref="K11:L11"/>
-    <mergeCell ref="K12:L12"/>
-    <mergeCell ref="I10:J10"/>
-    <mergeCell ref="I11:J11"/>
-    <mergeCell ref="I12:J12"/>
-    <mergeCell ref="K25:L25"/>
-    <mergeCell ref="I26:J26"/>
-    <mergeCell ref="K26:L26"/>
-    <mergeCell ref="I30:J30"/>
-    <mergeCell ref="K30:L30"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="I31:J31"/>
-    <mergeCell ref="E30:F30"/>
-    <mergeCell ref="E31:F31"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="K31:L31"/>
-    <mergeCell ref="K28:L28"/>
-    <mergeCell ref="K27:L27"/>
-    <mergeCell ref="I29:J29"/>
-    <mergeCell ref="K29:L29"/>
-    <mergeCell ref="C27:F27"/>
-    <mergeCell ref="I34:J34"/>
-    <mergeCell ref="K34:L34"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="E28:F28"/>
-    <mergeCell ref="E29:F29"/>
-    <mergeCell ref="E33:F33"/>
-    <mergeCell ref="I33:J33"/>
-    <mergeCell ref="C44:F44"/>
-    <mergeCell ref="I45:L45"/>
-    <mergeCell ref="I44:J44"/>
-    <mergeCell ref="K44:L44"/>
-    <mergeCell ref="C41:D41"/>
-    <mergeCell ref="E41:F41"/>
-    <mergeCell ref="C40:D40"/>
-    <mergeCell ref="C37:F37"/>
-    <mergeCell ref="I37:L37"/>
-    <mergeCell ref="E40:F40"/>
-    <mergeCell ref="C39:F39"/>
-    <mergeCell ref="C38:F38"/>
-    <mergeCell ref="I38:L38"/>
-    <mergeCell ref="I39:J39"/>
-    <mergeCell ref="K39:L39"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="I15:J15"/>
-    <mergeCell ref="K15:L15"/>
-    <mergeCell ref="C32:D32"/>
-    <mergeCell ref="E32:F32"/>
-    <mergeCell ref="I32:J32"/>
-    <mergeCell ref="K32:L32"/>
-    <mergeCell ref="K33:L33"/>
-    <mergeCell ref="C34:D34"/>
-    <mergeCell ref="E34:F34"/>
-    <mergeCell ref="C33:D33"/>
-    <mergeCell ref="I35:J35"/>
-    <mergeCell ref="K35:L35"/>
-    <mergeCell ref="I36:L36"/>
-    <mergeCell ref="C35:D35"/>
-    <mergeCell ref="E35:F35"/>
-    <mergeCell ref="C36:D36"/>
-    <mergeCell ref="E36:F36"/>
-    <mergeCell ref="C25:D25"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation allowBlank="1" showDropDown="1" showInputMessage="1" showErrorMessage="1" sqref="C6 I6"/>
@@ -7321,7 +7321,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>11</v>
@@ -7337,14 +7337,14 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A4" s="4" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="B4" s="5"/>
       <c r="C4" s="5"/>
       <c r="D4" s="6"/>
       <c r="E4" s="5"/>
       <c r="F4" s="62" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.4">
@@ -7352,7 +7352,7 @@
         <v>2</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="D5" s="8"/>
       <c r="E5" s="9" t="s">
@@ -7386,7 +7386,7 @@
       </c>
       <c r="D7" s="13"/>
       <c r="E7" s="14" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="F7" s="15" t="s">
         <v>7</v>
@@ -7394,13 +7394,13 @@
     </row>
     <row r="8" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A8" s="11" t="s">
-        <v>100</v>
-      </c>
-      <c r="C8" s="137" t="s">
-        <v>105</v>
-      </c>
-      <c r="D8" s="137"/>
-      <c r="E8" s="137"/>
+        <v>97</v>
+      </c>
+      <c r="C8" s="148" t="s">
+        <v>102</v>
+      </c>
+      <c r="D8" s="148"/>
+      <c r="E8" s="148"/>
     </row>
     <row r="9" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A9" s="16" t="s">
@@ -7423,32 +7423,32 @@
       <c r="B10" s="23">
         <v>4</v>
       </c>
-      <c r="C10" s="468"/>
-      <c r="D10" s="469"/>
-      <c r="E10" s="469"/>
-      <c r="F10" s="470"/>
+      <c r="C10" s="449"/>
+      <c r="D10" s="450"/>
+      <c r="E10" s="450"/>
+      <c r="F10" s="451"/>
     </row>
     <row r="11" spans="1:6" ht="32.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="24"/>
       <c r="B11" s="25">
         <v>5</v>
       </c>
-      <c r="C11" s="453" t="s">
-        <v>176</v>
-      </c>
-      <c r="D11" s="454"/>
-      <c r="E11" s="454"/>
-      <c r="F11" s="455"/>
+      <c r="C11" s="452" t="s">
+        <v>172</v>
+      </c>
+      <c r="D11" s="453"/>
+      <c r="E11" s="453"/>
+      <c r="F11" s="454"/>
     </row>
     <row r="12" spans="1:6" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A12" s="28"/>
       <c r="B12" s="29">
         <v>6</v>
       </c>
-      <c r="C12" s="471"/>
-      <c r="D12" s="472"/>
-      <c r="E12" s="472"/>
-      <c r="F12" s="473"/>
+      <c r="C12" s="455"/>
+      <c r="D12" s="456"/>
+      <c r="E12" s="456"/>
+      <c r="F12" s="457"/>
     </row>
     <row r="13" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="30" t="s">
@@ -7457,32 +7457,32 @@
       <c r="B13" s="23">
         <v>4</v>
       </c>
-      <c r="C13" s="474"/>
-      <c r="D13" s="475"/>
-      <c r="E13" s="475"/>
-      <c r="F13" s="476"/>
+      <c r="C13" s="458"/>
+      <c r="D13" s="459"/>
+      <c r="E13" s="459"/>
+      <c r="F13" s="460"/>
     </row>
     <row r="14" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="24"/>
       <c r="B14" s="25">
         <v>5</v>
       </c>
-      <c r="C14" s="453" t="s">
-        <v>88</v>
-      </c>
-      <c r="D14" s="454"/>
-      <c r="E14" s="454"/>
-      <c r="F14" s="455"/>
+      <c r="C14" s="452" t="s">
+        <v>85</v>
+      </c>
+      <c r="D14" s="453"/>
+      <c r="E14" s="453"/>
+      <c r="F14" s="454"/>
     </row>
     <row r="15" spans="1:6" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A15" s="32"/>
       <c r="B15" s="29">
         <v>6</v>
       </c>
-      <c r="C15" s="447"/>
-      <c r="D15" s="448"/>
-      <c r="E15" s="448"/>
-      <c r="F15" s="449"/>
+      <c r="C15" s="461"/>
+      <c r="D15" s="462"/>
+      <c r="E15" s="462"/>
+      <c r="F15" s="463"/>
     </row>
     <row r="16" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="30" t="s">
@@ -7491,32 +7491,32 @@
       <c r="B16" s="23">
         <v>4</v>
       </c>
-      <c r="C16" s="450"/>
-      <c r="D16" s="451"/>
-      <c r="E16" s="451"/>
-      <c r="F16" s="452"/>
+      <c r="C16" s="464"/>
+      <c r="D16" s="465"/>
+      <c r="E16" s="465"/>
+      <c r="F16" s="466"/>
     </row>
     <row r="17" spans="1:11" ht="22.15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="24"/>
       <c r="B17" s="25">
         <v>5</v>
       </c>
-      <c r="C17" s="453" t="s">
-        <v>89</v>
-      </c>
-      <c r="D17" s="454"/>
-      <c r="E17" s="454"/>
-      <c r="F17" s="455"/>
+      <c r="C17" s="452" t="s">
+        <v>86</v>
+      </c>
+      <c r="D17" s="453"/>
+      <c r="E17" s="453"/>
+      <c r="F17" s="454"/>
     </row>
     <row r="18" spans="1:11" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A18" s="32"/>
       <c r="B18" s="29">
         <v>6</v>
       </c>
-      <c r="C18" s="465"/>
-      <c r="D18" s="466"/>
-      <c r="E18" s="466"/>
-      <c r="F18" s="467"/>
+      <c r="C18" s="446"/>
+      <c r="D18" s="447"/>
+      <c r="E18" s="447"/>
+      <c r="F18" s="448"/>
       <c r="K18" s="53"/>
     </row>
     <row r="19" spans="1:11" ht="28.5" customHeight="1" x14ac:dyDescent="0.4">
@@ -7526,32 +7526,32 @@
       <c r="B19" s="23">
         <v>4</v>
       </c>
-      <c r="C19" s="477"/>
-      <c r="D19" s="478"/>
-      <c r="E19" s="478"/>
-      <c r="F19" s="479"/>
+      <c r="C19" s="467"/>
+      <c r="D19" s="468"/>
+      <c r="E19" s="468"/>
+      <c r="F19" s="469"/>
     </row>
     <row r="20" spans="1:11" ht="24.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="24"/>
       <c r="B20" s="25">
         <v>5</v>
       </c>
-      <c r="C20" s="453" t="s">
-        <v>91</v>
-      </c>
-      <c r="D20" s="454"/>
-      <c r="E20" s="454"/>
-      <c r="F20" s="455"/>
+      <c r="C20" s="452" t="s">
+        <v>88</v>
+      </c>
+      <c r="D20" s="453"/>
+      <c r="E20" s="453"/>
+      <c r="F20" s="454"/>
     </row>
     <row r="21" spans="1:11" ht="24.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A21" s="32"/>
       <c r="B21" s="29">
         <v>6</v>
       </c>
-      <c r="C21" s="465"/>
-      <c r="D21" s="466"/>
-      <c r="E21" s="466"/>
-      <c r="F21" s="467"/>
+      <c r="C21" s="446"/>
+      <c r="D21" s="447"/>
+      <c r="E21" s="447"/>
+      <c r="F21" s="448"/>
     </row>
     <row r="22" spans="1:11" ht="24.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="30" t="s">
@@ -7560,32 +7560,32 @@
       <c r="B22" s="23">
         <v>4</v>
       </c>
-      <c r="C22" s="450"/>
-      <c r="D22" s="451"/>
-      <c r="E22" s="451"/>
-      <c r="F22" s="452"/>
+      <c r="C22" s="464"/>
+      <c r="D22" s="465"/>
+      <c r="E22" s="465"/>
+      <c r="F22" s="466"/>
     </row>
     <row r="23" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="33"/>
       <c r="B23" s="25">
         <v>5</v>
       </c>
-      <c r="C23" s="453" t="s">
-        <v>87</v>
-      </c>
-      <c r="D23" s="454"/>
-      <c r="E23" s="454"/>
-      <c r="F23" s="455"/>
+      <c r="C23" s="452" t="s">
+        <v>84</v>
+      </c>
+      <c r="D23" s="453"/>
+      <c r="E23" s="453"/>
+      <c r="F23" s="454"/>
     </row>
     <row r="24" spans="1:11" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A24" s="35"/>
       <c r="B24" s="29">
         <v>6</v>
       </c>
-      <c r="C24" s="456"/>
-      <c r="D24" s="457"/>
-      <c r="E24" s="457"/>
-      <c r="F24" s="458"/>
+      <c r="C24" s="471"/>
+      <c r="D24" s="472"/>
+      <c r="E24" s="472"/>
+      <c r="F24" s="473"/>
     </row>
     <row r="25" spans="1:11" ht="23.45" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="36" t="s">
@@ -7594,38 +7594,38 @@
       <c r="B25" s="23">
         <v>4</v>
       </c>
-      <c r="C25" s="459"/>
-      <c r="D25" s="460"/>
-      <c r="E25" s="460"/>
-      <c r="F25" s="461"/>
+      <c r="C25" s="474"/>
+      <c r="D25" s="475"/>
+      <c r="E25" s="475"/>
+      <c r="F25" s="476"/>
     </row>
     <row r="26" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="37"/>
       <c r="B26" s="25">
         <v>5</v>
       </c>
-      <c r="C26" s="462"/>
-      <c r="D26" s="463"/>
-      <c r="E26" s="463"/>
-      <c r="F26" s="464"/>
+      <c r="C26" s="477"/>
+      <c r="D26" s="478"/>
+      <c r="E26" s="478"/>
+      <c r="F26" s="479"/>
     </row>
     <row r="27" spans="1:11" ht="22.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A27" s="39"/>
       <c r="B27" s="41"/>
-      <c r="C27" s="447"/>
-      <c r="D27" s="448"/>
-      <c r="E27" s="448"/>
-      <c r="F27" s="449"/>
+      <c r="C27" s="461"/>
+      <c r="D27" s="462"/>
+      <c r="E27" s="462"/>
+      <c r="F27" s="463"/>
     </row>
     <row r="28" spans="1:11" s="47" customFormat="1" ht="26.45" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="446" t="s">
-        <v>90</v>
-      </c>
-      <c r="B28" s="446"/>
-      <c r="C28" s="446"/>
-      <c r="D28" s="446"/>
-      <c r="E28" s="446"/>
-      <c r="F28" s="446"/>
+      <c r="A28" s="470" t="s">
+        <v>87</v>
+      </c>
+      <c r="B28" s="470"/>
+      <c r="C28" s="470"/>
+      <c r="D28" s="470"/>
+      <c r="E28" s="470"/>
+      <c r="F28" s="470"/>
     </row>
     <row r="29" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A29" s="40"/>
@@ -7653,6 +7653,13 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="A28:F28"/>
+    <mergeCell ref="C27:F27"/>
+    <mergeCell ref="C22:F22"/>
+    <mergeCell ref="C23:F23"/>
+    <mergeCell ref="C24:F24"/>
+    <mergeCell ref="C25:F25"/>
+    <mergeCell ref="C26:F26"/>
     <mergeCell ref="C8:E8"/>
     <mergeCell ref="C21:F21"/>
     <mergeCell ref="C10:F10"/>
@@ -7666,13 +7673,6 @@
     <mergeCell ref="C18:F18"/>
     <mergeCell ref="C19:F19"/>
     <mergeCell ref="C20:F20"/>
-    <mergeCell ref="A28:F28"/>
-    <mergeCell ref="C27:F27"/>
-    <mergeCell ref="C22:F22"/>
-    <mergeCell ref="C23:F23"/>
-    <mergeCell ref="C24:F24"/>
-    <mergeCell ref="C25:F25"/>
-    <mergeCell ref="C26:F26"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E5">
@@ -7724,7 +7724,7 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>11</v>
@@ -7740,14 +7740,14 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A4" s="4" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="B4" s="5"/>
       <c r="C4" s="5"/>
       <c r="D4" s="6"/>
       <c r="E4" s="5"/>
       <c r="F4" s="62" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.4">
@@ -7755,7 +7755,7 @@
         <v>2</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="D5" s="8"/>
       <c r="E5" s="9" t="s">
@@ -7797,13 +7797,13 @@
     </row>
     <row r="8" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A8" s="11" t="s">
-        <v>100</v>
-      </c>
-      <c r="C8" s="137" t="s">
-        <v>105</v>
-      </c>
-      <c r="D8" s="137"/>
-      <c r="E8" s="137"/>
+        <v>97</v>
+      </c>
+      <c r="C8" s="148" t="s">
+        <v>102</v>
+      </c>
+      <c r="D8" s="148"/>
+      <c r="E8" s="148"/>
     </row>
     <row r="9" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A9" s="16" t="s">
@@ -7826,32 +7826,32 @@
       <c r="B10" s="48">
         <v>4</v>
       </c>
-      <c r="C10" s="478"/>
-      <c r="D10" s="478"/>
-      <c r="E10" s="478"/>
-      <c r="F10" s="479"/>
+      <c r="C10" s="468"/>
+      <c r="D10" s="468"/>
+      <c r="E10" s="468"/>
+      <c r="F10" s="469"/>
     </row>
     <row r="11" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="24"/>
       <c r="B11" s="25">
         <v>5</v>
       </c>
-      <c r="C11" s="484" t="s">
-        <v>92</v>
-      </c>
-      <c r="D11" s="485"/>
-      <c r="E11" s="485"/>
-      <c r="F11" s="486"/>
+      <c r="C11" s="480" t="s">
+        <v>89</v>
+      </c>
+      <c r="D11" s="481"/>
+      <c r="E11" s="481"/>
+      <c r="F11" s="482"/>
     </row>
     <row r="12" spans="1:7" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A12" s="28"/>
       <c r="B12" s="29">
         <v>6</v>
       </c>
-      <c r="C12" s="490"/>
-      <c r="D12" s="491"/>
-      <c r="E12" s="491"/>
-      <c r="F12" s="492"/>
+      <c r="C12" s="483"/>
+      <c r="D12" s="484"/>
+      <c r="E12" s="484"/>
+      <c r="F12" s="485"/>
     </row>
     <row r="13" spans="1:7" ht="24.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="30" t="s">
@@ -7860,22 +7860,22 @@
       <c r="B13" s="23">
         <v>4</v>
       </c>
-      <c r="C13" s="474"/>
-      <c r="D13" s="475"/>
-      <c r="E13" s="475"/>
-      <c r="F13" s="476"/>
-    </row>
-    <row r="14" spans="1:7" ht="42.6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C13" s="458"/>
+      <c r="D13" s="459"/>
+      <c r="E13" s="459"/>
+      <c r="F13" s="460"/>
+    </row>
+    <row r="14" spans="1:7" ht="49.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="24"/>
       <c r="B14" s="25">
         <v>5</v>
       </c>
-      <c r="C14" s="453" t="s">
-        <v>177</v>
-      </c>
-      <c r="D14" s="454"/>
-      <c r="E14" s="454"/>
-      <c r="F14" s="455"/>
+      <c r="C14" s="452" t="s">
+        <v>173</v>
+      </c>
+      <c r="D14" s="453"/>
+      <c r="E14" s="453"/>
+      <c r="F14" s="454"/>
       <c r="G14" s="59"/>
     </row>
     <row r="15" spans="1:7" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
@@ -7883,10 +7883,10 @@
       <c r="B15" s="29">
         <v>6</v>
       </c>
-      <c r="C15" s="447"/>
-      <c r="D15" s="448"/>
-      <c r="E15" s="448"/>
-      <c r="F15" s="449"/>
+      <c r="C15" s="461"/>
+      <c r="D15" s="462"/>
+      <c r="E15" s="462"/>
+      <c r="F15" s="463"/>
     </row>
     <row r="16" spans="1:7" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="30" t="s">
@@ -7895,32 +7895,32 @@
       <c r="B16" s="23">
         <v>4</v>
       </c>
-      <c r="C16" s="450"/>
-      <c r="D16" s="451"/>
-      <c r="E16" s="451"/>
-      <c r="F16" s="452"/>
+      <c r="C16" s="464"/>
+      <c r="D16" s="465"/>
+      <c r="E16" s="465"/>
+      <c r="F16" s="466"/>
     </row>
     <row r="17" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="24"/>
       <c r="B17" s="25">
         <v>5</v>
       </c>
-      <c r="C17" s="453" t="s">
-        <v>179</v>
-      </c>
-      <c r="D17" s="454"/>
-      <c r="E17" s="454"/>
-      <c r="F17" s="455"/>
+      <c r="C17" s="452" t="s">
+        <v>175</v>
+      </c>
+      <c r="D17" s="453"/>
+      <c r="E17" s="453"/>
+      <c r="F17" s="454"/>
     </row>
     <row r="18" spans="1:11" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A18" s="32"/>
       <c r="B18" s="29">
         <v>6</v>
       </c>
-      <c r="C18" s="447"/>
-      <c r="D18" s="448"/>
-      <c r="E18" s="448"/>
-      <c r="F18" s="449"/>
+      <c r="C18" s="461"/>
+      <c r="D18" s="462"/>
+      <c r="E18" s="462"/>
+      <c r="F18" s="463"/>
     </row>
     <row r="19" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="30" t="s">
@@ -7929,32 +7929,32 @@
       <c r="B19" s="23">
         <v>4</v>
       </c>
-      <c r="C19" s="477"/>
-      <c r="D19" s="478"/>
-      <c r="E19" s="478"/>
-      <c r="F19" s="479"/>
+      <c r="C19" s="467"/>
+      <c r="D19" s="468"/>
+      <c r="E19" s="468"/>
+      <c r="F19" s="469"/>
     </row>
     <row r="20" spans="1:11" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="24"/>
       <c r="B20" s="25">
         <v>5</v>
       </c>
-      <c r="C20" s="484" t="s">
-        <v>199</v>
-      </c>
-      <c r="D20" s="485"/>
-      <c r="E20" s="485"/>
-      <c r="F20" s="486"/>
+      <c r="C20" s="480" t="s">
+        <v>201</v>
+      </c>
+      <c r="D20" s="481"/>
+      <c r="E20" s="481"/>
+      <c r="F20" s="482"/>
     </row>
     <row r="21" spans="1:11" ht="24.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A21" s="32"/>
       <c r="B21" s="29">
         <v>6</v>
       </c>
-      <c r="C21" s="465"/>
-      <c r="D21" s="466"/>
-      <c r="E21" s="466"/>
-      <c r="F21" s="467"/>
+      <c r="C21" s="446"/>
+      <c r="D21" s="447"/>
+      <c r="E21" s="447"/>
+      <c r="F21" s="448"/>
       <c r="K21" s="49"/>
     </row>
     <row r="22" spans="1:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -7964,32 +7964,32 @@
       <c r="B22" s="23">
         <v>4</v>
       </c>
-      <c r="C22" s="481"/>
-      <c r="D22" s="482"/>
-      <c r="E22" s="482"/>
-      <c r="F22" s="483"/>
+      <c r="C22" s="487"/>
+      <c r="D22" s="488"/>
+      <c r="E22" s="488"/>
+      <c r="F22" s="489"/>
     </row>
     <row r="23" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="33"/>
       <c r="B23" s="25">
         <v>5</v>
       </c>
-      <c r="C23" s="484" t="s">
-        <v>178</v>
-      </c>
-      <c r="D23" s="485"/>
-      <c r="E23" s="485"/>
-      <c r="F23" s="486"/>
+      <c r="C23" s="480" t="s">
+        <v>174</v>
+      </c>
+      <c r="D23" s="481"/>
+      <c r="E23" s="481"/>
+      <c r="F23" s="482"/>
     </row>
     <row r="24" spans="1:11" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A24" s="35"/>
       <c r="B24" s="29">
         <v>6</v>
       </c>
-      <c r="C24" s="456"/>
-      <c r="D24" s="457"/>
-      <c r="E24" s="457"/>
-      <c r="F24" s="458"/>
+      <c r="C24" s="471"/>
+      <c r="D24" s="472"/>
+      <c r="E24" s="472"/>
+      <c r="F24" s="473"/>
     </row>
     <row r="25" spans="1:11" ht="26.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="36" t="s">
@@ -7998,40 +7998,40 @@
       <c r="B25" s="23">
         <v>4</v>
       </c>
-      <c r="C25" s="481"/>
-      <c r="D25" s="482"/>
-      <c r="E25" s="482"/>
-      <c r="F25" s="483"/>
+      <c r="C25" s="487"/>
+      <c r="D25" s="488"/>
+      <c r="E25" s="488"/>
+      <c r="F25" s="489"/>
     </row>
     <row r="26" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="37"/>
       <c r="B26" s="25">
         <v>5</v>
       </c>
-      <c r="C26" s="487" t="s">
-        <v>180</v>
-      </c>
-      <c r="D26" s="488"/>
-      <c r="E26" s="488"/>
-      <c r="F26" s="489"/>
+      <c r="C26" s="490" t="s">
+        <v>176</v>
+      </c>
+      <c r="D26" s="491"/>
+      <c r="E26" s="491"/>
+      <c r="F26" s="492"/>
     </row>
     <row r="27" spans="1:11" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A27" s="39"/>
       <c r="B27" s="41"/>
-      <c r="C27" s="447"/>
-      <c r="D27" s="448"/>
-      <c r="E27" s="448"/>
-      <c r="F27" s="449"/>
+      <c r="C27" s="461"/>
+      <c r="D27" s="462"/>
+      <c r="E27" s="462"/>
+      <c r="F27" s="463"/>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A28" s="480" t="s">
+      <c r="A28" s="486" t="s">
         <v>26</v>
       </c>
-      <c r="B28" s="480"/>
-      <c r="C28" s="480"/>
-      <c r="D28" s="480"/>
-      <c r="E28" s="480"/>
-      <c r="F28" s="480"/>
+      <c r="B28" s="486"/>
+      <c r="C28" s="486"/>
+      <c r="D28" s="486"/>
+      <c r="E28" s="486"/>
+      <c r="F28" s="486"/>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A29" s="2" t="s">
@@ -8051,6 +8051,13 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="A28:F28"/>
+    <mergeCell ref="C27:F27"/>
+    <mergeCell ref="C22:F22"/>
+    <mergeCell ref="C23:F23"/>
+    <mergeCell ref="C24:F24"/>
+    <mergeCell ref="C25:F25"/>
+    <mergeCell ref="C26:F26"/>
     <mergeCell ref="C8:E8"/>
     <mergeCell ref="C21:F21"/>
     <mergeCell ref="C10:F10"/>
@@ -8064,13 +8071,6 @@
     <mergeCell ref="C18:F18"/>
     <mergeCell ref="C19:F19"/>
     <mergeCell ref="C20:F20"/>
-    <mergeCell ref="A28:F28"/>
-    <mergeCell ref="C27:F27"/>
-    <mergeCell ref="C22:F22"/>
-    <mergeCell ref="C23:F23"/>
-    <mergeCell ref="C24:F24"/>
-    <mergeCell ref="C25:F25"/>
-    <mergeCell ref="C26:F26"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation allowBlank="1" showDropDown="1" showInputMessage="1" showErrorMessage="1" sqref="C6"/>
@@ -8122,7 +8122,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>11</v>
@@ -8138,14 +8138,14 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A4" s="4" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="B4" s="5"/>
       <c r="C4" s="5"/>
       <c r="D4" s="6"/>
       <c r="E4" s="5"/>
       <c r="F4" s="62" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.4">
@@ -8153,7 +8153,7 @@
         <v>2</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="D5" s="8"/>
       <c r="E5" s="9" t="s">
@@ -8195,13 +8195,13 @@
     </row>
     <row r="8" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A8" s="11" t="s">
-        <v>100</v>
-      </c>
-      <c r="C8" s="496" t="s">
-        <v>106</v>
-      </c>
-      <c r="D8" s="496"/>
-      <c r="E8" s="496"/>
+        <v>97</v>
+      </c>
+      <c r="C8" s="493" t="s">
+        <v>103</v>
+      </c>
+      <c r="D8" s="493"/>
+      <c r="E8" s="493"/>
     </row>
     <row r="9" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A9" s="16" t="s">
@@ -8224,32 +8224,32 @@
       <c r="B10" s="23">
         <v>3</v>
       </c>
-      <c r="C10" s="500"/>
-      <c r="D10" s="501"/>
-      <c r="E10" s="501"/>
-      <c r="F10" s="502"/>
+      <c r="C10" s="497"/>
+      <c r="D10" s="498"/>
+      <c r="E10" s="498"/>
+      <c r="F10" s="499"/>
     </row>
     <row r="11" spans="1:6" ht="25.15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="24"/>
       <c r="B11" s="25">
         <v>4</v>
       </c>
-      <c r="C11" s="453" t="s">
-        <v>181</v>
-      </c>
-      <c r="D11" s="454"/>
-      <c r="E11" s="454"/>
-      <c r="F11" s="455"/>
+      <c r="C11" s="452" t="s">
+        <v>177</v>
+      </c>
+      <c r="D11" s="453"/>
+      <c r="E11" s="453"/>
+      <c r="F11" s="454"/>
     </row>
     <row r="12" spans="1:6" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A12" s="28"/>
       <c r="B12" s="29">
         <v>5</v>
       </c>
-      <c r="C12" s="497"/>
-      <c r="D12" s="498"/>
-      <c r="E12" s="498"/>
-      <c r="F12" s="499"/>
+      <c r="C12" s="494"/>
+      <c r="D12" s="495"/>
+      <c r="E12" s="495"/>
+      <c r="F12" s="496"/>
     </row>
     <row r="13" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="30" t="s">
@@ -8258,32 +8258,32 @@
       <c r="B13" s="23">
         <v>3</v>
       </c>
-      <c r="C13" s="503"/>
-      <c r="D13" s="504"/>
-      <c r="E13" s="504"/>
-      <c r="F13" s="505"/>
+      <c r="C13" s="500"/>
+      <c r="D13" s="501"/>
+      <c r="E13" s="501"/>
+      <c r="F13" s="502"/>
     </row>
     <row r="14" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="24"/>
       <c r="B14" s="25">
         <v>4</v>
       </c>
-      <c r="C14" s="453" t="s">
-        <v>94</v>
-      </c>
-      <c r="D14" s="454"/>
-      <c r="E14" s="454"/>
-      <c r="F14" s="455"/>
+      <c r="C14" s="452" t="s">
+        <v>91</v>
+      </c>
+      <c r="D14" s="453"/>
+      <c r="E14" s="453"/>
+      <c r="F14" s="454"/>
     </row>
     <row r="15" spans="1:6" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A15" s="32"/>
       <c r="B15" s="29">
         <v>5</v>
       </c>
-      <c r="C15" s="506"/>
-      <c r="D15" s="507"/>
-      <c r="E15" s="507"/>
-      <c r="F15" s="508"/>
+      <c r="C15" s="503"/>
+      <c r="D15" s="504"/>
+      <c r="E15" s="504"/>
+      <c r="F15" s="505"/>
     </row>
     <row r="16" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="30" t="s">
@@ -8292,32 +8292,32 @@
       <c r="B16" s="23">
         <v>3</v>
       </c>
-      <c r="C16" s="481"/>
-      <c r="D16" s="482"/>
-      <c r="E16" s="482"/>
-      <c r="F16" s="483"/>
+      <c r="C16" s="487"/>
+      <c r="D16" s="488"/>
+      <c r="E16" s="488"/>
+      <c r="F16" s="489"/>
     </row>
     <row r="17" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="24"/>
       <c r="B17" s="25">
         <v>4</v>
       </c>
-      <c r="C17" s="453" t="s">
-        <v>93</v>
-      </c>
-      <c r="D17" s="454"/>
-      <c r="E17" s="454"/>
-      <c r="F17" s="455"/>
+      <c r="C17" s="452" t="s">
+        <v>90</v>
+      </c>
+      <c r="D17" s="453"/>
+      <c r="E17" s="453"/>
+      <c r="F17" s="454"/>
     </row>
     <row r="18" spans="1:6" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A18" s="32"/>
       <c r="B18" s="29">
         <v>5</v>
       </c>
-      <c r="C18" s="506"/>
-      <c r="D18" s="507"/>
-      <c r="E18" s="507"/>
-      <c r="F18" s="508"/>
+      <c r="C18" s="503"/>
+      <c r="D18" s="504"/>
+      <c r="E18" s="504"/>
+      <c r="F18" s="505"/>
     </row>
     <row r="19" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="30" t="s">
@@ -8326,32 +8326,32 @@
       <c r="B19" s="23">
         <v>3</v>
       </c>
-      <c r="C19" s="459"/>
-      <c r="D19" s="460"/>
-      <c r="E19" s="460"/>
-      <c r="F19" s="461"/>
+      <c r="C19" s="474"/>
+      <c r="D19" s="475"/>
+      <c r="E19" s="475"/>
+      <c r="F19" s="476"/>
     </row>
     <row r="20" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="24"/>
       <c r="B20" s="25">
         <v>4</v>
       </c>
-      <c r="C20" s="453" t="s">
-        <v>182</v>
-      </c>
-      <c r="D20" s="454"/>
-      <c r="E20" s="454"/>
-      <c r="F20" s="455"/>
+      <c r="C20" s="452" t="s">
+        <v>178</v>
+      </c>
+      <c r="D20" s="453"/>
+      <c r="E20" s="453"/>
+      <c r="F20" s="454"/>
     </row>
     <row r="21" spans="1:6" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A21" s="32"/>
       <c r="B21" s="29">
         <v>5</v>
       </c>
-      <c r="C21" s="497"/>
-      <c r="D21" s="498"/>
-      <c r="E21" s="498"/>
-      <c r="F21" s="499"/>
+      <c r="C21" s="494"/>
+      <c r="D21" s="495"/>
+      <c r="E21" s="495"/>
+      <c r="F21" s="496"/>
     </row>
     <row r="22" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="30" t="s">
@@ -8360,32 +8360,32 @@
       <c r="B22" s="23">
         <v>3</v>
       </c>
-      <c r="C22" s="481"/>
-      <c r="D22" s="482"/>
-      <c r="E22" s="482"/>
-      <c r="F22" s="483"/>
+      <c r="C22" s="487"/>
+      <c r="D22" s="488"/>
+      <c r="E22" s="488"/>
+      <c r="F22" s="489"/>
     </row>
     <row r="23" spans="1:6" ht="38.450000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="33"/>
       <c r="B23" s="25">
         <v>4</v>
       </c>
-      <c r="C23" s="453" t="s">
-        <v>95</v>
-      </c>
-      <c r="D23" s="454"/>
-      <c r="E23" s="454"/>
-      <c r="F23" s="455"/>
+      <c r="C23" s="452" t="s">
+        <v>92</v>
+      </c>
+      <c r="D23" s="453"/>
+      <c r="E23" s="453"/>
+      <c r="F23" s="454"/>
     </row>
     <row r="24" spans="1:6" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A24" s="35"/>
       <c r="B24" s="29">
         <v>5</v>
       </c>
-      <c r="C24" s="456"/>
-      <c r="D24" s="457"/>
-      <c r="E24" s="457"/>
-      <c r="F24" s="458"/>
+      <c r="C24" s="471"/>
+      <c r="D24" s="472"/>
+      <c r="E24" s="472"/>
+      <c r="F24" s="473"/>
     </row>
     <row r="25" spans="1:6" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="36" t="s">
@@ -8394,38 +8394,38 @@
       <c r="B25" s="23">
         <v>2</v>
       </c>
-      <c r="C25" s="459"/>
-      <c r="D25" s="460"/>
-      <c r="E25" s="460"/>
-      <c r="F25" s="461"/>
+      <c r="C25" s="474"/>
+      <c r="D25" s="475"/>
+      <c r="E25" s="475"/>
+      <c r="F25" s="476"/>
     </row>
     <row r="26" spans="1:6" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="37"/>
       <c r="B26" s="25">
         <v>3</v>
       </c>
-      <c r="C26" s="493"/>
-      <c r="D26" s="494"/>
-      <c r="E26" s="494"/>
-      <c r="F26" s="495"/>
+      <c r="C26" s="506"/>
+      <c r="D26" s="507"/>
+      <c r="E26" s="507"/>
+      <c r="F26" s="508"/>
     </row>
     <row r="27" spans="1:6" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A27" s="39"/>
       <c r="B27" s="41"/>
-      <c r="C27" s="447"/>
-      <c r="D27" s="448"/>
-      <c r="E27" s="448"/>
-      <c r="F27" s="449"/>
+      <c r="C27" s="461"/>
+      <c r="D27" s="462"/>
+      <c r="E27" s="462"/>
+      <c r="F27" s="463"/>
     </row>
     <row r="28" spans="1:6" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A28" s="480" t="s">
+      <c r="A28" s="486" t="s">
         <v>26</v>
       </c>
-      <c r="B28" s="480"/>
-      <c r="C28" s="480"/>
-      <c r="D28" s="480"/>
-      <c r="E28" s="480"/>
-      <c r="F28" s="480"/>
+      <c r="B28" s="486"/>
+      <c r="C28" s="486"/>
+      <c r="D28" s="486"/>
+      <c r="E28" s="486"/>
+      <c r="F28" s="486"/>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A29" s="2" t="s">
@@ -8445,6 +8445,13 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="A28:F28"/>
+    <mergeCell ref="C27:F27"/>
+    <mergeCell ref="C22:F22"/>
+    <mergeCell ref="C23:F23"/>
+    <mergeCell ref="C24:F24"/>
+    <mergeCell ref="C25:F25"/>
+    <mergeCell ref="C26:F26"/>
     <mergeCell ref="C8:E8"/>
     <mergeCell ref="C21:F21"/>
     <mergeCell ref="C10:F10"/>
@@ -8458,13 +8465,6 @@
     <mergeCell ref="C18:F18"/>
     <mergeCell ref="C19:F19"/>
     <mergeCell ref="C20:F20"/>
-    <mergeCell ref="A28:F28"/>
-    <mergeCell ref="C27:F27"/>
-    <mergeCell ref="C22:F22"/>
-    <mergeCell ref="C23:F23"/>
-    <mergeCell ref="C24:F24"/>
-    <mergeCell ref="C25:F25"/>
-    <mergeCell ref="C26:F26"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E5">
